--- a/data/raw/Democracy in Action/review/dia_2008_labor_review.xlsx
+++ b/data/raw/Democracy in Action/review/dia_2008_labor_review.xlsx
@@ -9,17 +9,23 @@
     <sheet name="review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$W$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$Y$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="400">
   <si>
     <t xml:space="preserve">row_id</t>
   </si>
   <si>
+    <t xml:space="preserve">review_action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">review_note</t>
+  </si>
+  <si>
     <t xml:space="preserve">contest_id</t>
   </si>
   <si>
@@ -87,6 +93,9 @@
   </si>
   <si>
     <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">2008D</t>
@@ -1551,28 +1560,30 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="17.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="40.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="32.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="21.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="16.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="40.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="13.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="18.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="18.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="40.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="11.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="80.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="13.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="17.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="22.71" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="40.71" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="40.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="40.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="40.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="32.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="21.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="10.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="16.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="40.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="13.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="18.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="40.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="11.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="80.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="13.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="17.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="22.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="40.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="40.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1645,4171 +1656,4615 @@
       <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="O2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
       <c r="R3" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
       <c r="R4" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U4" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y4" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
       <c r="R5" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U5" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y5" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U6" s="1"/>
+        <v>63</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y6" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
       <c r="R7" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U7" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y7" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
       <c r="R8" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U8" s="1"/>
+        <v>75</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y8" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
       <c r="R9" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U9" s="1"/>
+        <v>81</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y9" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J10" s="1"/>
-      <c r="K10" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
       <c r="R10" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U10" s="1"/>
+        <v>87</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y10" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J11" s="1"/>
-      <c r="K11" s="1" t="s">
-        <v>88</v>
-      </c>
+      <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
       <c r="R11" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U11" s="1"/>
+        <v>93</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y11" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
       <c r="R12" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U12" s="1"/>
+        <v>99</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y12" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
       <c r="R13" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U13" s="1"/>
+        <v>105</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y13" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>106</v>
-      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
       <c r="M14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
       <c r="R14" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J15" s="1"/>
-      <c r="K15" s="1" t="s">
-        <v>112</v>
-      </c>
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
       <c r="R15" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U15" s="1"/>
+        <v>117</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y15" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="1" t="s">
-        <v>118</v>
-      </c>
+      <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
       <c r="R16" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="1" t="s">
-        <v>125</v>
-      </c>
+      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="N17" s="1"/>
       <c r="O17" s="1" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="U17" s="1"/>
+        <v>132</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V17" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J18" s="1"/>
-      <c r="K18" s="1" t="s">
-        <v>135</v>
-      </c>
+      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N18" s="1"/>
       <c r="O18" s="1" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="U18" s="1"/>
+        <v>140</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V18" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
+      </c>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J19" s="1"/>
-      <c r="K19" s="1" t="s">
-        <v>142</v>
-      </c>
+      <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
       <c r="R19" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="U19" s="1"/>
+        <v>147</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V19" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y19" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>147</v>
+        <v>29</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J20" s="1"/>
-      <c r="K20" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="U20" s="1"/>
+        <v>153</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y20" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>153</v>
+        <v>29</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J21" s="1"/>
-      <c r="K21" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
       <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
       <c r="R21" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="U21" s="1"/>
+        <v>159</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V21" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y21" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="W21" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>159</v>
+        <v>29</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J22" s="1"/>
-      <c r="K22" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
       <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
       <c r="R22" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="U22" s="1"/>
+        <v>164</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V22" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>154</v>
+        <v>133</v>
+      </c>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>164</v>
+        <v>29</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J23" s="1"/>
-      <c r="K23" s="1" t="s">
-        <v>165</v>
-      </c>
+      <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
       <c r="R23" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="U23" s="1"/>
+        <v>170</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V23" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>169</v>
+        <v>133</v>
+      </c>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J24" s="1"/>
-      <c r="K24" s="1" t="s">
-        <v>172</v>
-      </c>
+      <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
       <c r="R24" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="U24" s="1"/>
+        <v>177</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y24" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="W24" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="1" t="s">
-        <v>178</v>
-      </c>
+      <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N25" s="1"/>
       <c r="O25" s="1" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="U25" s="1"/>
+        <v>183</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V25" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="W25" s="1" t="s">
-        <v>182</v>
+        <v>133</v>
+      </c>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>184</v>
+        <v>29</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J26" s="1"/>
-      <c r="K26" s="1" t="s">
-        <v>185</v>
-      </c>
+      <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
       <c r="R26" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="U26" s="1"/>
+        <v>190</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V26" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="W26" s="1" t="s">
-        <v>189</v>
+        <v>133</v>
+      </c>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J27" s="1"/>
-      <c r="K27" s="1" t="s">
-        <v>185</v>
-      </c>
+      <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
       <c r="R27" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="U27" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V27" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="W27" s="1" t="s">
-        <v>185</v>
+        <v>133</v>
+      </c>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>197</v>
+        <v>29</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+        <v>199</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J28" s="1"/>
-      <c r="K28" s="1" t="s">
-        <v>198</v>
-      </c>
+      <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1" t="s">
-        <v>31</v>
+        <v>201</v>
       </c>
       <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
       <c r="R28" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="U28" s="1"/>
+        <v>203</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V28" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="W28" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
+      </c>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J29" s="1"/>
-      <c r="K29" s="1" t="s">
-        <v>205</v>
-      </c>
+      <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1" t="s">
-        <v>31</v>
+        <v>208</v>
       </c>
       <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
       <c r="R29" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T29" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y29" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="W29" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J30" s="1"/>
-      <c r="K30" s="1" t="s">
-        <v>210</v>
-      </c>
+      <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1" t="s">
-        <v>31</v>
+        <v>213</v>
       </c>
       <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1" t="s">
+      <c r="O30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V30" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="Q30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="W30" s="1" t="s">
-        <v>210</v>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="I31" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J31" s="1"/>
-      <c r="K31" s="1" t="s">
-        <v>210</v>
-      </c>
+      <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1" t="s">
-        <v>31</v>
+        <v>213</v>
       </c>
       <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
       <c r="R31" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U31" s="1"/>
+        <v>218</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V31" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="W31" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
+      </c>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>217</v>
+        <v>29</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J32" s="1"/>
-      <c r="K32" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
       <c r="R32" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1" t="s">
-        <v>100</v>
+        <v>222</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>221</v>
+        <v>26</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>99</v>
+        <v>225</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+        <v>226</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="J33" s="1"/>
-      <c r="K33" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="U33" s="1"/>
+        <v>228</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="V33" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y33" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="W33" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>229</v>
+        <v>29</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
+        <v>231</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J34" s="1"/>
-      <c r="K34" s="1" t="s">
-        <v>231</v>
-      </c>
+      <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1" t="s">
-        <v>31</v>
+        <v>234</v>
       </c>
       <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
+      <c r="O34" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>232</v>
-      </c>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
       <c r="S34" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T34" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>237</v>
+        <v>29</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+        <v>231</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J35" s="1"/>
-      <c r="K35" s="1" t="s">
-        <v>238</v>
-      </c>
+      <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
-        <v>31</v>
+        <v>241</v>
       </c>
       <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
       <c r="R35" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="V35" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="W35" s="1" t="s">
         <v>238</v>
       </c>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+        <v>231</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J36" s="1"/>
-      <c r="K36" s="1" t="s">
-        <v>243</v>
-      </c>
+      <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>31</v>
+        <v>246</v>
       </c>
       <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
+      <c r="O36" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P36" s="1"/>
-      <c r="Q36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>244</v>
-      </c>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
       <c r="S36" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="V36" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="W36" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
+      </c>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>246</v>
+        <v>29</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+        <v>231</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J37" s="1"/>
-      <c r="K37" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>31</v>
+        <v>250</v>
       </c>
       <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="V37" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="W37" s="1" t="s">
-        <v>247</v>
+        <v>238</v>
+      </c>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>251</v>
+        <v>29</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
+        <v>231</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J38" s="1"/>
-      <c r="K38" s="1" t="s">
-        <v>252</v>
-      </c>
+      <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
-        <v>31</v>
+        <v>255</v>
       </c>
       <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
       <c r="R38" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="U38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>257</v>
+        <v>29</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+        <v>231</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J39" s="1"/>
-      <c r="K39" s="1" t="s">
-        <v>258</v>
-      </c>
+      <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1" t="s">
-        <v>31</v>
+        <v>261</v>
       </c>
       <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
+      <c r="O39" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P39" s="1"/>
-      <c r="Q39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>259</v>
-      </c>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
       <c r="S39" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="V39" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="W39" s="1" t="s">
-        <v>258</v>
+        <v>238</v>
+      </c>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J40" s="1"/>
-      <c r="K40" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>262</v>
-      </c>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
+        <v>250</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P40" s="1"/>
-      <c r="Q40" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>263</v>
-      </c>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
       <c r="S40" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>36</v>
+        <v>266</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="V40" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="W40" s="1" t="s">
-        <v>247</v>
+        <v>267</v>
+      </c>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="N41" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F41" s="1" t="s">
+      <c r="O41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T41" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="U41" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="V41" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="W41" s="1" t="s">
-        <v>247</v>
+        <v>267</v>
+      </c>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>268</v>
+        <v>29</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J42" s="1"/>
-      <c r="K42" s="1" t="s">
-        <v>269</v>
-      </c>
+      <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1" t="s">
-        <v>31</v>
+        <v>272</v>
       </c>
       <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
       <c r="R42" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>36</v>
+        <v>274</v>
       </c>
       <c r="U42" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>274</v>
+        <v>29</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J43" s="1"/>
-      <c r="K43" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1" t="s">
+      <c r="O43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W43" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="Q43" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1" t="s">
-        <v>64</v>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J44" s="1"/>
-      <c r="K44" s="1" t="s">
-        <v>279</v>
-      </c>
+      <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
-        <v>31</v>
+        <v>282</v>
       </c>
       <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
+      <c r="O44" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
       <c r="S44" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>36</v>
+        <v>283</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="V44" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="W44" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
+      </c>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>282</v>
+        <v>29</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J45" s="1"/>
-      <c r="K45" s="1" t="s">
-        <v>283</v>
-      </c>
+      <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1" t="s">
-        <v>31</v>
+        <v>286</v>
       </c>
       <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
+      <c r="O45" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P45" s="1"/>
-      <c r="Q45" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R45" s="1" t="s">
-        <v>284</v>
-      </c>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
       <c r="S45" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>36</v>
+        <v>287</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="V45" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="W45" s="1" t="s">
-        <v>283</v>
+        <v>267</v>
+      </c>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>286</v>
+        <v>29</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J46" s="1"/>
-      <c r="K46" s="1" t="s">
-        <v>287</v>
-      </c>
+      <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="s">
-        <v>31</v>
+        <v>290</v>
       </c>
       <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
+      <c r="O46" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P46" s="1"/>
-      <c r="Q46" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R46" s="1" t="s">
-        <v>288</v>
-      </c>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
       <c r="S46" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>36</v>
+        <v>291</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="V46" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="W46" s="1" t="s">
-        <v>287</v>
+        <v>267</v>
+      </c>
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>290</v>
+        <v>29</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J47" s="1"/>
-      <c r="K47" s="1" t="s">
-        <v>269</v>
-      </c>
+      <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1" t="s">
-        <v>31</v>
+        <v>272</v>
       </c>
       <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O47" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
       <c r="R47" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>208</v>
+        <v>295</v>
       </c>
       <c r="U47" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V47" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="W47" s="1" t="s">
-        <v>269</v>
+        <v>296</v>
+      </c>
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J48" s="1"/>
-      <c r="K48" s="1" t="s">
-        <v>252</v>
-      </c>
+      <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1" t="s">
-        <v>31</v>
+        <v>255</v>
       </c>
       <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q48" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O48" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
       <c r="R48" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>208</v>
+        <v>300</v>
       </c>
       <c r="U48" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="V48" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V48" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="W48" s="1" t="s">
-        <v>252</v>
+        <v>301</v>
+      </c>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>300</v>
+        <v>29</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J49" s="1"/>
-      <c r="K49" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O49" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
       <c r="R49" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S49" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="U49" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V49" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V49" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="W49" s="1" t="s">
-        <v>76</v>
+        <v>296</v>
+      </c>
+      <c r="X49" s="1"/>
+      <c r="Y49" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>304</v>
+        <v>29</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J50" s="1"/>
-      <c r="K50" s="1" t="s">
-        <v>252</v>
-      </c>
+      <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1" t="s">
-        <v>31</v>
+        <v>255</v>
       </c>
       <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
+      <c r="O50" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P50" s="1"/>
-      <c r="Q50" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R50" s="1" t="s">
-        <v>305</v>
-      </c>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
       <c r="S50" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>208</v>
+        <v>308</v>
       </c>
       <c r="U50" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V50" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V50" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="W50" s="1" t="s">
-        <v>252</v>
+        <v>296</v>
+      </c>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>307</v>
+        <v>29</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J51" s="1"/>
-      <c r="K51" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>309</v>
-      </c>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
       <c r="R51" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="S51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T51" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W51" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="S51" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T51" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U51" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V51" s="1"/>
-      <c r="W51" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L52" s="1" t="s">
+      <c r="S52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T52" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="M52" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R52" s="1" t="s">
+      <c r="U52" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V52" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W52" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="S52" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T52" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U52" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V52" s="1"/>
-      <c r="W52" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>316</v>
+        <v>29</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J53" s="1"/>
-      <c r="K53" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>317</v>
-      </c>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="S53" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T53" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U53" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V53" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W53" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="S53" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T53" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U53" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V53" s="1"/>
-      <c r="W53" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>319</v>
+        <v>29</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J54" s="1"/>
-      <c r="K54" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>320</v>
-      </c>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
       <c r="M54" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
       <c r="R54" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="S54" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U54" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V54" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W54" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T54" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U54" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V54" s="1"/>
-      <c r="W54" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>322</v>
+        <v>29</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J55" s="1"/>
-      <c r="K55" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>323</v>
-      </c>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
       <c r="M55" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
       <c r="R55" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U55" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V55" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W55" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T55" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U55" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V55" s="1"/>
-      <c r="W55" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>325</v>
+        <v>29</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J56" s="1"/>
-      <c r="K56" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>326</v>
-      </c>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
       <c r="M56" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
       <c r="R56" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W56" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T56" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U56" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V56" s="1"/>
-      <c r="W56" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>328</v>
+        <v>29</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J57" s="1"/>
-      <c r="K57" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>329</v>
-      </c>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
       <c r="R57" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T57" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U57" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V57" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W57" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U57" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V57" s="1"/>
-      <c r="W57" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>331</v>
+        <v>29</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J58" s="1"/>
-      <c r="K58" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>332</v>
-      </c>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
       <c r="R58" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="S58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T58" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U58" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V58" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W58" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="S58" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T58" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U58" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V58" s="1"/>
-      <c r="W58" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>334</v>
+        <v>29</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J59" s="1"/>
-      <c r="K59" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>335</v>
-      </c>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
       <c r="M59" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q59" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1"/>
       <c r="R59" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="S59" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T59" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W59" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="S59" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T59" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U59" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V59" s="1"/>
-      <c r="W59" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>337</v>
+        <v>29</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J60" s="1"/>
-      <c r="K60" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>338</v>
-      </c>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
       <c r="R60" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T60" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U60" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="W60" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="S60" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T60" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U60" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="V60" s="1"/>
-      <c r="W60" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>340</v>
+        <v>29</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J61" s="1"/>
-      <c r="K61" s="1" t="s">
-        <v>341</v>
-      </c>
+      <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>31</v>
+        <v>344</v>
       </c>
       <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O61" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P61" s="1"/>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="S61" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>130</v>
+        <v>346</v>
       </c>
       <c r="U61" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="W61" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="V61" s="1"/>
-      <c r="W61" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>346</v>
+        <v>29</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J62" s="1"/>
-      <c r="K62" s="1" t="s">
-        <v>347</v>
-      </c>
+      <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1" t="s">
-        <v>31</v>
+        <v>350</v>
       </c>
       <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
+      <c r="O62" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P62" s="1"/>
-      <c r="Q62" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R62" s="1" t="s">
-        <v>348</v>
-      </c>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
       <c r="S62" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>130</v>
+        <v>351</v>
       </c>
       <c r="U62" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V62" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W62" s="1" t="s">
         <v>347</v>
       </c>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>350</v>
+        <v>29</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J63" s="1"/>
-      <c r="K63" s="1" t="s">
-        <v>351</v>
-      </c>
+      <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1" t="s">
-        <v>31</v>
+        <v>354</v>
       </c>
       <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O63" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
       <c r="R63" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="S63" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>130</v>
+        <v>356</v>
       </c>
       <c r="U63" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V63" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W63" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
+      </c>
+      <c r="X63" s="1"/>
+      <c r="Y63" s="1" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>334</v>
+        <v>29</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J64" s="1"/>
-      <c r="K64" s="1" t="s">
-        <v>355</v>
-      </c>
+      <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="N64" s="1"/>
       <c r="O64" s="1" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>356</v>
+        <v>129</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="S64" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>130</v>
+        <v>360</v>
       </c>
       <c r="U64" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V64" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W64" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
+      </c>
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>307</v>
+        <v>29</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J65" s="1"/>
-      <c r="K65" s="1" t="s">
-        <v>178</v>
-      </c>
+      <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N65" s="1"/>
       <c r="O65" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="P65" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="Q65" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R65" s="1" t="s">
-        <v>359</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="R65" s="1"/>
       <c r="S65" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>130</v>
+        <v>362</v>
       </c>
       <c r="U65" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V65" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W65" s="1" t="s">
-        <v>178</v>
+        <v>347</v>
+      </c>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>361</v>
+        <v>29</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J66" s="1"/>
-      <c r="K66" s="1" t="s">
-        <v>185</v>
-      </c>
+      <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O66" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
       <c r="R66" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>130</v>
+        <v>366</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V66" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W66" s="1" t="s">
-        <v>185</v>
+        <v>347</v>
+      </c>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>365</v>
+        <v>29</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J67" s="1"/>
-      <c r="K67" s="1" t="s">
-        <v>269</v>
-      </c>
+      <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1" t="s">
-        <v>31</v>
+        <v>272</v>
       </c>
       <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
+      <c r="O67" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P67" s="1"/>
-      <c r="Q67" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>366</v>
-      </c>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
       <c r="S67" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>130</v>
+        <v>369</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V67" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V67" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W67" s="1" t="s">
-        <v>269</v>
+        <v>347</v>
+      </c>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>368</v>
+        <v>29</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J68" s="1"/>
-      <c r="K68" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1" t="s">
-        <v>31</v>
+        <v>372</v>
       </c>
       <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O68" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
       <c r="R68" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="S68" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>130</v>
+        <v>374</v>
       </c>
       <c r="U68" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V68" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V68" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W68" s="1" t="s">
-        <v>369</v>
+        <v>347</v>
+      </c>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>373</v>
+        <v>29</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J69" s="1"/>
-      <c r="K69" s="1" t="s">
-        <v>374</v>
-      </c>
+      <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1" t="s">
-        <v>31</v>
+        <v>377</v>
       </c>
       <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O69" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
       <c r="R69" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>130</v>
+        <v>379</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V69" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V69" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W69" s="1" t="s">
-        <v>374</v>
+        <v>347</v>
+      </c>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>378</v>
+        <v>29</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J70" s="1"/>
-      <c r="K70" s="1" t="s">
-        <v>379</v>
-      </c>
+      <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1" t="s">
-        <v>31</v>
+        <v>382</v>
       </c>
       <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
+      <c r="O70" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P70" s="1"/>
-      <c r="Q70" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R70" s="1" t="s">
-        <v>380</v>
-      </c>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
       <c r="S70" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>130</v>
+        <v>383</v>
       </c>
       <c r="U70" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V70" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V70" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W70" s="1" t="s">
-        <v>379</v>
+        <v>347</v>
+      </c>
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>382</v>
+        <v>29</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J71" s="1"/>
-      <c r="K71" s="1" t="s">
-        <v>252</v>
-      </c>
+      <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1" t="s">
-        <v>31</v>
+        <v>255</v>
       </c>
       <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
+      <c r="O71" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P71" s="1"/>
-      <c r="Q71" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>383</v>
-      </c>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
       <c r="S71" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>130</v>
+        <v>386</v>
       </c>
       <c r="U71" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V71" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V71" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W71" s="1" t="s">
-        <v>252</v>
+        <v>347</v>
+      </c>
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>385</v>
+        <v>29</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J72" s="1"/>
-      <c r="K72" s="1" t="s">
-        <v>308</v>
-      </c>
+      <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1" t="s">
-        <v>31</v>
+        <v>311</v>
       </c>
       <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="Q72" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O72" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1"/>
       <c r="R72" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="S72" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="U72" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V72" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V72" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W72" s="1" t="s">
-        <v>308</v>
+        <v>347</v>
+      </c>
+      <c r="X72" s="1"/>
+      <c r="Y72" s="1" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>389</v>
+        <v>29</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J73" s="1"/>
-      <c r="K73" s="1" t="s">
-        <v>88</v>
-      </c>
+      <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
-      <c r="P73" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="Q73" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="O73" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P73" s="1"/>
+      <c r="Q73" s="1"/>
       <c r="R73" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="S73" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>130</v>
+        <v>394</v>
       </c>
       <c r="U73" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="V73" s="1"/>
+        <v>236</v>
+      </c>
+      <c r="V73" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="W73" s="1" t="s">
-        <v>88</v>
+        <v>347</v>
+      </c>
+      <c r="X73" s="1"/>
+      <c r="Y73" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>393</v>
+        <v>28</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>394</v>
+        <v>29</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
+        <v>396</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
-      <c r="M74" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="M74" s="1"/>
       <c r="N74" s="1"/>
-      <c r="O74" s="1"/>
+      <c r="O74" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P74" s="1"/>
-      <c r="Q74" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R74" s="1" t="s">
-        <v>395</v>
-      </c>
+      <c r="Q74" s="1"/>
+      <c r="R74" s="1"/>
       <c r="S74" s="1" t="s">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="U74" s="1"/>
-      <c r="V74" s="1"/>
+        <v>398</v>
+      </c>
+      <c r="U74" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V74" s="1" t="s">
+        <v>399</v>
+      </c>
       <c r="W74" s="1"/>
+      <c r="X74" s="1"/>
+      <c r="Y74" s="1"/>
     </row>
     <row r="75">
       <c r="A75" s="1"/>
@@ -5835,6 +6290,8 @@
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
+      <c r="X75" s="1"/>
+      <c r="Y75" s="1"/>
     </row>
     <row r="76">
       <c r="A76" s="1"/>
@@ -5860,6 +6317,8 @@
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
+      <c r="X76" s="1"/>
+      <c r="Y76" s="1"/>
     </row>
     <row r="77">
       <c r="A77" s="1"/>
@@ -5885,6 +6344,8 @@
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
       <c r="W77" s="1"/>
+      <c r="X77" s="1"/>
+      <c r="Y77" s="1"/>
     </row>
     <row r="78">
       <c r="A78" s="1"/>
@@ -5910,6 +6371,8 @@
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
+      <c r="X78" s="1"/>
+      <c r="Y78" s="1"/>
     </row>
     <row r="79">
       <c r="A79" s="1"/>
@@ -5935,6 +6398,8 @@
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
+      <c r="X79" s="1"/>
+      <c r="Y79" s="1"/>
     </row>
     <row r="80">
       <c r="A80" s="1"/>
@@ -5960,6 +6425,8 @@
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
+      <c r="X80" s="1"/>
+      <c r="Y80" s="1"/>
     </row>
     <row r="81">
       <c r="A81" s="1"/>
@@ -5985,6 +6452,8 @@
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
+      <c r="X81" s="1"/>
+      <c r="Y81" s="1"/>
     </row>
     <row r="82">
       <c r="A82" s="1"/>
@@ -6010,6 +6479,8 @@
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
+      <c r="X82" s="1"/>
+      <c r="Y82" s="1"/>
     </row>
     <row r="83">
       <c r="A83" s="1"/>
@@ -6035,6 +6506,8 @@
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
+      <c r="X83" s="1"/>
+      <c r="Y83" s="1"/>
     </row>
     <row r="84">
       <c r="A84" s="1"/>
@@ -6060,6 +6533,8 @@
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
+      <c r="X84" s="1"/>
+      <c r="Y84" s="1"/>
     </row>
     <row r="85">
       <c r="A85" s="1"/>
@@ -6085,6 +6560,8 @@
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
+      <c r="X85" s="1"/>
+      <c r="Y85" s="1"/>
     </row>
     <row r="86">
       <c r="A86" s="1"/>
@@ -6110,6 +6587,8 @@
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
+      <c r="X86" s="1"/>
+      <c r="Y86" s="1"/>
     </row>
     <row r="87">
       <c r="A87" s="1"/>
@@ -6135,6 +6614,8 @@
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
+      <c r="X87" s="1"/>
+      <c r="Y87" s="1"/>
     </row>
     <row r="88">
       <c r="A88" s="1"/>
@@ -6160,6 +6641,8 @@
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
+      <c r="X88" s="1"/>
+      <c r="Y88" s="1"/>
     </row>
     <row r="89">
       <c r="A89" s="1"/>
@@ -6185,6 +6668,8 @@
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
+      <c r="X89" s="1"/>
+      <c r="Y89" s="1"/>
     </row>
     <row r="90">
       <c r="A90" s="1"/>
@@ -6210,6 +6695,8 @@
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
+      <c r="X90" s="1"/>
+      <c r="Y90" s="1"/>
     </row>
     <row r="91">
       <c r="A91" s="1"/>
@@ -6235,6 +6722,8 @@
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
+      <c r="X91" s="1"/>
+      <c r="Y91" s="1"/>
     </row>
     <row r="92">
       <c r="A92" s="1"/>
@@ -6260,6 +6749,8 @@
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
+      <c r="X92" s="1"/>
+      <c r="Y92" s="1"/>
     </row>
     <row r="93">
       <c r="A93" s="1"/>
@@ -6285,6 +6776,8 @@
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
+      <c r="X93" s="1"/>
+      <c r="Y93" s="1"/>
     </row>
     <row r="94">
       <c r="A94" s="1"/>
@@ -6310,6 +6803,8 @@
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
+      <c r="X94" s="1"/>
+      <c r="Y94" s="1"/>
     </row>
     <row r="95">
       <c r="A95" s="1"/>
@@ -6335,6 +6830,8 @@
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
+      <c r="X95" s="1"/>
+      <c r="Y95" s="1"/>
     </row>
     <row r="96">
       <c r="A96" s="1"/>
@@ -6360,6 +6857,8 @@
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
+      <c r="X96" s="1"/>
+      <c r="Y96" s="1"/>
     </row>
     <row r="97">
       <c r="A97" s="1"/>
@@ -6385,6 +6884,8 @@
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
+      <c r="X97" s="1"/>
+      <c r="Y97" s="1"/>
     </row>
     <row r="98">
       <c r="A98" s="1"/>
@@ -6410,6 +6911,8 @@
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
       <c r="W98" s="1"/>
+      <c r="X98" s="1"/>
+      <c r="Y98" s="1"/>
     </row>
     <row r="99">
       <c r="A99" s="1"/>
@@ -6435,6 +6938,8 @@
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
+      <c r="X99" s="1"/>
+      <c r="Y99" s="1"/>
     </row>
     <row r="100">
       <c r="A100" s="1"/>
@@ -6460,6 +6965,8 @@
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
+      <c r="X100" s="1"/>
+      <c r="Y100" s="1"/>
     </row>
     <row r="101">
       <c r="A101" s="1"/>
@@ -6485,6 +6992,8 @@
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
+      <c r="X101" s="1"/>
+      <c r="Y101" s="1"/>
     </row>
     <row r="102">
       <c r="A102" s="1"/>
@@ -6510,6 +7019,8 @@
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
+      <c r="X102" s="1"/>
+      <c r="Y102" s="1"/>
     </row>
     <row r="103">
       <c r="A103" s="1"/>
@@ -6535,6 +7046,8 @@
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
+      <c r="X103" s="1"/>
+      <c r="Y103" s="1"/>
     </row>
     <row r="104">
       <c r="A104" s="1"/>
@@ -6560,6 +7073,8 @@
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
+      <c r="X104" s="1"/>
+      <c r="Y104" s="1"/>
     </row>
     <row r="105">
       <c r="A105" s="1"/>
@@ -6585,6 +7100,8 @@
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
+      <c r="X105" s="1"/>
+      <c r="Y105" s="1"/>
     </row>
     <row r="106">
       <c r="A106" s="1"/>
@@ -6610,6 +7127,8 @@
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
+      <c r="X106" s="1"/>
+      <c r="Y106" s="1"/>
     </row>
     <row r="107">
       <c r="A107" s="1"/>
@@ -6635,6 +7154,8 @@
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
+      <c r="X107" s="1"/>
+      <c r="Y107" s="1"/>
     </row>
     <row r="108">
       <c r="A108" s="1"/>
@@ -6660,6 +7181,8 @@
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
+      <c r="X108" s="1"/>
+      <c r="Y108" s="1"/>
     </row>
     <row r="109">
       <c r="A109" s="1"/>
@@ -6685,6 +7208,8 @@
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
+      <c r="X109" s="1"/>
+      <c r="Y109" s="1"/>
     </row>
     <row r="110">
       <c r="A110" s="1"/>
@@ -6710,6 +7235,8 @@
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
+      <c r="X110" s="1"/>
+      <c r="Y110" s="1"/>
     </row>
     <row r="111">
       <c r="A111" s="1"/>
@@ -6735,6 +7262,8 @@
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
+      <c r="X111" s="1"/>
+      <c r="Y111" s="1"/>
     </row>
     <row r="112">
       <c r="A112" s="1"/>
@@ -6760,6 +7289,8 @@
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
+      <c r="X112" s="1"/>
+      <c r="Y112" s="1"/>
     </row>
     <row r="113">
       <c r="A113" s="1"/>
@@ -6785,6 +7316,8 @@
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
+      <c r="X113" s="1"/>
+      <c r="Y113" s="1"/>
     </row>
     <row r="114">
       <c r="A114" s="1"/>
@@ -6810,6 +7343,8 @@
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
+      <c r="X114" s="1"/>
+      <c r="Y114" s="1"/>
     </row>
     <row r="115">
       <c r="A115" s="1"/>
@@ -6835,6 +7370,8 @@
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
+      <c r="X115" s="1"/>
+      <c r="Y115" s="1"/>
     </row>
     <row r="116">
       <c r="A116" s="1"/>
@@ -6860,6 +7397,8 @@
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
+      <c r="X116" s="1"/>
+      <c r="Y116" s="1"/>
     </row>
     <row r="117">
       <c r="A117" s="1"/>
@@ -6885,6 +7424,8 @@
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
+      <c r="X117" s="1"/>
+      <c r="Y117" s="1"/>
     </row>
     <row r="118">
       <c r="A118" s="1"/>
@@ -6910,6 +7451,8 @@
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
+      <c r="X118" s="1"/>
+      <c r="Y118" s="1"/>
     </row>
     <row r="119">
       <c r="A119" s="1"/>
@@ -6935,6 +7478,8 @@
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
+      <c r="X119" s="1"/>
+      <c r="Y119" s="1"/>
     </row>
     <row r="120">
       <c r="A120" s="1"/>
@@ -6960,6 +7505,8 @@
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
+      <c r="X120" s="1"/>
+      <c r="Y120" s="1"/>
     </row>
     <row r="121">
       <c r="A121" s="1"/>
@@ -6985,6 +7532,8 @@
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
+      <c r="X121" s="1"/>
+      <c r="Y121" s="1"/>
     </row>
     <row r="122">
       <c r="A122" s="1"/>
@@ -7010,6 +7559,8 @@
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
+      <c r="X122" s="1"/>
+      <c r="Y122" s="1"/>
     </row>
     <row r="123">
       <c r="A123" s="1"/>
@@ -7035,6 +7586,8 @@
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
+      <c r="X123" s="1"/>
+      <c r="Y123" s="1"/>
     </row>
     <row r="124">
       <c r="A124" s="1"/>
@@ -7060,6 +7613,8 @@
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
+      <c r="X124" s="1"/>
+      <c r="Y124" s="1"/>
     </row>
     <row r="125">
       <c r="A125" s="1"/>
@@ -7085,6 +7640,8 @@
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
+      <c r="X125" s="1"/>
+      <c r="Y125" s="1"/>
     </row>
     <row r="126">
       <c r="A126" s="1"/>
@@ -7110,6 +7667,8 @@
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
+      <c r="X126" s="1"/>
+      <c r="Y126" s="1"/>
     </row>
     <row r="127">
       <c r="A127" s="1"/>
@@ -7135,6 +7694,8 @@
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
+      <c r="X127" s="1"/>
+      <c r="Y127" s="1"/>
     </row>
     <row r="128">
       <c r="A128" s="1"/>
@@ -7160,6 +7721,8 @@
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
+      <c r="X128" s="1"/>
+      <c r="Y128" s="1"/>
     </row>
     <row r="129">
       <c r="A129" s="1"/>
@@ -7185,6 +7748,8 @@
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
+      <c r="X129" s="1"/>
+      <c r="Y129" s="1"/>
     </row>
     <row r="130">
       <c r="A130" s="1"/>
@@ -7210,6 +7775,8 @@
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
+      <c r="X130" s="1"/>
+      <c r="Y130" s="1"/>
     </row>
     <row r="131">
       <c r="A131" s="1"/>
@@ -7235,6 +7802,8 @@
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
+      <c r="X131" s="1"/>
+      <c r="Y131" s="1"/>
     </row>
     <row r="132">
       <c r="A132" s="1"/>
@@ -7260,6 +7829,8 @@
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
+      <c r="X132" s="1"/>
+      <c r="Y132" s="1"/>
     </row>
     <row r="133">
       <c r="A133" s="1"/>
@@ -7285,6 +7856,8 @@
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
+      <c r="X133" s="1"/>
+      <c r="Y133" s="1"/>
     </row>
     <row r="134">
       <c r="A134" s="1"/>
@@ -7310,6 +7883,8 @@
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
+      <c r="X134" s="1"/>
+      <c r="Y134" s="1"/>
     </row>
     <row r="135">
       <c r="A135" s="1"/>
@@ -7335,6 +7910,8 @@
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
+      <c r="X135" s="1"/>
+      <c r="Y135" s="1"/>
     </row>
     <row r="136">
       <c r="A136" s="1"/>
@@ -7360,6 +7937,8 @@
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
+      <c r="X136" s="1"/>
+      <c r="Y136" s="1"/>
     </row>
     <row r="137">
       <c r="A137" s="1"/>
@@ -7385,6 +7964,8 @@
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
+      <c r="X137" s="1"/>
+      <c r="Y137" s="1"/>
     </row>
     <row r="138">
       <c r="A138" s="1"/>
@@ -7410,6 +7991,8 @@
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
+      <c r="X138" s="1"/>
+      <c r="Y138" s="1"/>
     </row>
     <row r="139">
       <c r="A139" s="1"/>
@@ -7435,6 +8018,8 @@
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
+      <c r="X139" s="1"/>
+      <c r="Y139" s="1"/>
     </row>
     <row r="140">
       <c r="A140" s="1"/>
@@ -7460,6 +8045,8 @@
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
+      <c r="X140" s="1"/>
+      <c r="Y140" s="1"/>
     </row>
     <row r="141">
       <c r="A141" s="1"/>
@@ -7485,6 +8072,8 @@
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
+      <c r="X141" s="1"/>
+      <c r="Y141" s="1"/>
     </row>
     <row r="142">
       <c r="A142" s="1"/>
@@ -7510,6 +8099,8 @@
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
+      <c r="X142" s="1"/>
+      <c r="Y142" s="1"/>
     </row>
     <row r="143">
       <c r="A143" s="1"/>
@@ -7535,6 +8126,8 @@
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
+      <c r="X143" s="1"/>
+      <c r="Y143" s="1"/>
     </row>
     <row r="144">
       <c r="A144" s="1"/>
@@ -7560,6 +8153,8 @@
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
+      <c r="X144" s="1"/>
+      <c r="Y144" s="1"/>
     </row>
     <row r="145">
       <c r="A145" s="1"/>
@@ -7585,6 +8180,8 @@
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
+      <c r="X145" s="1"/>
+      <c r="Y145" s="1"/>
     </row>
     <row r="146">
       <c r="A146" s="1"/>
@@ -7610,6 +8207,8 @@
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
+      <c r="X146" s="1"/>
+      <c r="Y146" s="1"/>
     </row>
     <row r="147">
       <c r="A147" s="1"/>
@@ -7635,6 +8234,8 @@
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
+      <c r="X147" s="1"/>
+      <c r="Y147" s="1"/>
     </row>
     <row r="148">
       <c r="A148" s="1"/>
@@ -7660,6 +8261,8 @@
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
+      <c r="X148" s="1"/>
+      <c r="Y148" s="1"/>
     </row>
     <row r="149">
       <c r="A149" s="1"/>
@@ -7685,6 +8288,8 @@
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
+      <c r="X149" s="1"/>
+      <c r="Y149" s="1"/>
     </row>
     <row r="150">
       <c r="A150" s="1"/>
@@ -7710,6 +8315,8 @@
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
+      <c r="X150" s="1"/>
+      <c r="Y150" s="1"/>
     </row>
     <row r="151">
       <c r="A151" s="1"/>
@@ -7735,6 +8342,8 @@
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
+      <c r="X151" s="1"/>
+      <c r="Y151" s="1"/>
     </row>
     <row r="152">
       <c r="A152" s="1"/>
@@ -7760,6 +8369,8 @@
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
+      <c r="X152" s="1"/>
+      <c r="Y152" s="1"/>
     </row>
     <row r="153">
       <c r="A153" s="1"/>
@@ -7785,6 +8396,8 @@
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
+      <c r="X153" s="1"/>
+      <c r="Y153" s="1"/>
     </row>
     <row r="154">
       <c r="A154" s="1"/>
@@ -7810,6 +8423,8 @@
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
+      <c r="X154" s="1"/>
+      <c r="Y154" s="1"/>
     </row>
     <row r="155">
       <c r="A155" s="1"/>
@@ -7835,6 +8450,8 @@
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
+      <c r="X155" s="1"/>
+      <c r="Y155" s="1"/>
     </row>
     <row r="156">
       <c r="A156" s="1"/>
@@ -7860,6 +8477,8 @@
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
+      <c r="X156" s="1"/>
+      <c r="Y156" s="1"/>
     </row>
     <row r="157">
       <c r="A157" s="1"/>
@@ -7885,6 +8504,8 @@
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
+      <c r="X157" s="1"/>
+      <c r="Y157" s="1"/>
     </row>
     <row r="158">
       <c r="A158" s="1"/>
@@ -7910,6 +8531,8 @@
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
+      <c r="X158" s="1"/>
+      <c r="Y158" s="1"/>
     </row>
     <row r="159">
       <c r="A159" s="1"/>
@@ -7935,6 +8558,8 @@
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
+      <c r="X159" s="1"/>
+      <c r="Y159" s="1"/>
     </row>
     <row r="160">
       <c r="A160" s="1"/>
@@ -7960,6 +8585,8 @@
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
+      <c r="X160" s="1"/>
+      <c r="Y160" s="1"/>
     </row>
     <row r="161">
       <c r="A161" s="1"/>
@@ -7985,6 +8612,8 @@
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
+      <c r="X161" s="1"/>
+      <c r="Y161" s="1"/>
     </row>
     <row r="162">
       <c r="A162" s="1"/>
@@ -8010,6 +8639,8 @@
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
+      <c r="X162" s="1"/>
+      <c r="Y162" s="1"/>
     </row>
     <row r="163">
       <c r="A163" s="1"/>
@@ -8035,6 +8666,8 @@
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
+      <c r="X163" s="1"/>
+      <c r="Y163" s="1"/>
     </row>
     <row r="164">
       <c r="A164" s="1"/>
@@ -8060,6 +8693,8 @@
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
+      <c r="X164" s="1"/>
+      <c r="Y164" s="1"/>
     </row>
     <row r="165">
       <c r="A165" s="1"/>
@@ -8085,6 +8720,8 @@
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
       <c r="W165" s="1"/>
+      <c r="X165" s="1"/>
+      <c r="Y165" s="1"/>
     </row>
     <row r="166">
       <c r="A166" s="1"/>
@@ -8110,6 +8747,8 @@
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
+      <c r="X166" s="1"/>
+      <c r="Y166" s="1"/>
     </row>
     <row r="167">
       <c r="A167" s="1"/>
@@ -8135,6 +8774,8 @@
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
+      <c r="X167" s="1"/>
+      <c r="Y167" s="1"/>
     </row>
     <row r="168">
       <c r="A168" s="1"/>
@@ -8160,6 +8801,8 @@
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
+      <c r="X168" s="1"/>
+      <c r="Y168" s="1"/>
     </row>
     <row r="169">
       <c r="A169" s="1"/>
@@ -8185,6 +8828,8 @@
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
+      <c r="X169" s="1"/>
+      <c r="Y169" s="1"/>
     </row>
     <row r="170">
       <c r="A170" s="1"/>
@@ -8210,6 +8855,8 @@
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
+      <c r="X170" s="1"/>
+      <c r="Y170" s="1"/>
     </row>
     <row r="171">
       <c r="A171" s="1"/>
@@ -8235,6 +8882,8 @@
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
+      <c r="X171" s="1"/>
+      <c r="Y171" s="1"/>
     </row>
     <row r="172">
       <c r="A172" s="1"/>
@@ -8260,6 +8909,8 @@
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
+      <c r="X172" s="1"/>
+      <c r="Y172" s="1"/>
     </row>
     <row r="173">
       <c r="A173" s="1"/>
@@ -8285,6 +8936,8 @@
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
+      <c r="X173" s="1"/>
+      <c r="Y173" s="1"/>
     </row>
     <row r="174">
       <c r="A174" s="1"/>
@@ -8310,6 +8963,8 @@
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
+      <c r="X174" s="1"/>
+      <c r="Y174" s="1"/>
     </row>
     <row r="175">
       <c r="A175" s="1"/>
@@ -8335,6 +8990,8 @@
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
+      <c r="X175" s="1"/>
+      <c r="Y175" s="1"/>
     </row>
     <row r="176">
       <c r="A176" s="1"/>
@@ -8360,6 +9017,8 @@
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
+      <c r="X176" s="1"/>
+      <c r="Y176" s="1"/>
     </row>
     <row r="177">
       <c r="A177" s="1"/>
@@ -8385,6 +9044,8 @@
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
+      <c r="X177" s="1"/>
+      <c r="Y177" s="1"/>
     </row>
     <row r="178">
       <c r="A178" s="1"/>
@@ -8410,6 +9071,8 @@
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
+      <c r="X178" s="1"/>
+      <c r="Y178" s="1"/>
     </row>
     <row r="179">
       <c r="A179" s="1"/>
@@ -8435,6 +9098,8 @@
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
+      <c r="X179" s="1"/>
+      <c r="Y179" s="1"/>
     </row>
     <row r="180">
       <c r="A180" s="1"/>
@@ -8460,6 +9125,8 @@
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
+      <c r="X180" s="1"/>
+      <c r="Y180" s="1"/>
     </row>
     <row r="181">
       <c r="A181" s="1"/>
@@ -8485,6 +9152,8 @@
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
+      <c r="X181" s="1"/>
+      <c r="Y181" s="1"/>
     </row>
     <row r="182">
       <c r="A182" s="1"/>
@@ -8510,6 +9179,8 @@
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
+      <c r="X182" s="1"/>
+      <c r="Y182" s="1"/>
     </row>
     <row r="183">
       <c r="A183" s="1"/>
@@ -8535,6 +9206,8 @@
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
+      <c r="X183" s="1"/>
+      <c r="Y183" s="1"/>
     </row>
     <row r="184">
       <c r="A184" s="1"/>
@@ -8560,6 +9233,8 @@
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
+      <c r="X184" s="1"/>
+      <c r="Y184" s="1"/>
     </row>
     <row r="185">
       <c r="A185" s="1"/>
@@ -8585,6 +9260,8 @@
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
+      <c r="X185" s="1"/>
+      <c r="Y185" s="1"/>
     </row>
     <row r="186">
       <c r="A186" s="1"/>
@@ -8610,6 +9287,8 @@
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
       <c r="W186" s="1"/>
+      <c r="X186" s="1"/>
+      <c r="Y186" s="1"/>
     </row>
     <row r="187">
       <c r="A187" s="1"/>
@@ -8635,6 +9314,8 @@
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
       <c r="W187" s="1"/>
+      <c r="X187" s="1"/>
+      <c r="Y187" s="1"/>
     </row>
     <row r="188">
       <c r="A188" s="1"/>
@@ -8660,6 +9341,8 @@
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
       <c r="W188" s="1"/>
+      <c r="X188" s="1"/>
+      <c r="Y188" s="1"/>
     </row>
     <row r="189">
       <c r="A189" s="1"/>
@@ -8685,6 +9368,8 @@
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
       <c r="W189" s="1"/>
+      <c r="X189" s="1"/>
+      <c r="Y189" s="1"/>
     </row>
     <row r="190">
       <c r="A190" s="1"/>
@@ -8710,6 +9395,8 @@
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
       <c r="W190" s="1"/>
+      <c r="X190" s="1"/>
+      <c r="Y190" s="1"/>
     </row>
     <row r="191">
       <c r="A191" s="1"/>
@@ -8735,6 +9422,8 @@
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
       <c r="W191" s="1"/>
+      <c r="X191" s="1"/>
+      <c r="Y191" s="1"/>
     </row>
     <row r="192">
       <c r="A192" s="1"/>
@@ -8760,6 +9449,8 @@
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
       <c r="W192" s="1"/>
+      <c r="X192" s="1"/>
+      <c r="Y192" s="1"/>
     </row>
     <row r="193">
       <c r="A193" s="1"/>
@@ -8785,6 +9476,8 @@
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
       <c r="W193" s="1"/>
+      <c r="X193" s="1"/>
+      <c r="Y193" s="1"/>
     </row>
     <row r="194">
       <c r="A194" s="1"/>
@@ -8810,6 +9503,8 @@
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
+      <c r="X194" s="1"/>
+      <c r="Y194" s="1"/>
     </row>
     <row r="195">
       <c r="A195" s="1"/>
@@ -8835,6 +9530,8 @@
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
       <c r="W195" s="1"/>
+      <c r="X195" s="1"/>
+      <c r="Y195" s="1"/>
     </row>
     <row r="196">
       <c r="A196" s="1"/>
@@ -8860,6 +9557,8 @@
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
       <c r="W196" s="1"/>
+      <c r="X196" s="1"/>
+      <c r="Y196" s="1"/>
     </row>
     <row r="197">
       <c r="A197" s="1"/>
@@ -8885,6 +9584,8 @@
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
       <c r="W197" s="1"/>
+      <c r="X197" s="1"/>
+      <c r="Y197" s="1"/>
     </row>
     <row r="198">
       <c r="A198" s="1"/>
@@ -8910,6 +9611,8 @@
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
+      <c r="X198" s="1"/>
+      <c r="Y198" s="1"/>
     </row>
     <row r="199">
       <c r="A199" s="1"/>
@@ -8935,6 +9638,8 @@
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
+      <c r="X199" s="1"/>
+      <c r="Y199" s="1"/>
     </row>
     <row r="200">
       <c r="A200" s="1"/>
@@ -8960,6 +9665,8 @@
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
       <c r="W200" s="1"/>
+      <c r="X200" s="1"/>
+      <c r="Y200" s="1"/>
     </row>
     <row r="201">
       <c r="A201" s="1"/>
@@ -8985,6 +9692,8 @@
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
+      <c r="X201" s="1"/>
+      <c r="Y201" s="1"/>
     </row>
     <row r="202">
       <c r="A202" s="1"/>
@@ -9010,6 +9719,8 @@
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
       <c r="W202" s="1"/>
+      <c r="X202" s="1"/>
+      <c r="Y202" s="1"/>
     </row>
     <row r="203">
       <c r="A203" s="1"/>
@@ -9035,6 +9746,8 @@
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
       <c r="W203" s="1"/>
+      <c r="X203" s="1"/>
+      <c r="Y203" s="1"/>
     </row>
     <row r="204">
       <c r="A204" s="1"/>
@@ -9060,6 +9773,8 @@
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
+      <c r="X204" s="1"/>
+      <c r="Y204" s="1"/>
     </row>
     <row r="205">
       <c r="A205" s="1"/>
@@ -9085,6 +9800,8 @@
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
       <c r="W205" s="1"/>
+      <c r="X205" s="1"/>
+      <c r="Y205" s="1"/>
     </row>
     <row r="206">
       <c r="A206" s="1"/>
@@ -9110,6 +9827,8 @@
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
       <c r="W206" s="1"/>
+      <c r="X206" s="1"/>
+      <c r="Y206" s="1"/>
     </row>
     <row r="207">
       <c r="A207" s="1"/>
@@ -9135,6 +9854,8 @@
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
+      <c r="X207" s="1"/>
+      <c r="Y207" s="1"/>
     </row>
     <row r="208">
       <c r="A208" s="1"/>
@@ -9160,6 +9881,8 @@
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
       <c r="W208" s="1"/>
+      <c r="X208" s="1"/>
+      <c r="Y208" s="1"/>
     </row>
     <row r="209">
       <c r="A209" s="1"/>
@@ -9185,6 +9908,8 @@
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
       <c r="W209" s="1"/>
+      <c r="X209" s="1"/>
+      <c r="Y209" s="1"/>
     </row>
     <row r="210">
       <c r="A210" s="1"/>
@@ -9210,6 +9935,8 @@
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
+      <c r="X210" s="1"/>
+      <c r="Y210" s="1"/>
     </row>
     <row r="211">
       <c r="A211" s="1"/>
@@ -9235,6 +9962,8 @@
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
+      <c r="X211" s="1"/>
+      <c r="Y211" s="1"/>
     </row>
     <row r="212">
       <c r="A212" s="1"/>
@@ -9260,6 +9989,8 @@
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
+      <c r="X212" s="1"/>
+      <c r="Y212" s="1"/>
     </row>
     <row r="213">
       <c r="A213" s="1"/>
@@ -9285,6 +10016,8 @@
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
+      <c r="X213" s="1"/>
+      <c r="Y213" s="1"/>
     </row>
     <row r="214">
       <c r="A214" s="1"/>
@@ -9310,6 +10043,8 @@
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
       <c r="W214" s="1"/>
+      <c r="X214" s="1"/>
+      <c r="Y214" s="1"/>
     </row>
     <row r="215">
       <c r="A215" s="1"/>
@@ -9335,6 +10070,8 @@
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
+      <c r="X215" s="1"/>
+      <c r="Y215" s="1"/>
     </row>
     <row r="216">
       <c r="A216" s="1"/>
@@ -9360,6 +10097,8 @@
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
+      <c r="X216" s="1"/>
+      <c r="Y216" s="1"/>
     </row>
     <row r="217">
       <c r="A217" s="1"/>
@@ -9385,6 +10124,8 @@
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
+      <c r="X217" s="1"/>
+      <c r="Y217" s="1"/>
     </row>
     <row r="218">
       <c r="A218" s="1"/>
@@ -9410,6 +10151,8 @@
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
+      <c r="X218" s="1"/>
+      <c r="Y218" s="1"/>
     </row>
     <row r="219">
       <c r="A219" s="1"/>
@@ -9435,6 +10178,8 @@
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
+      <c r="X219" s="1"/>
+      <c r="Y219" s="1"/>
     </row>
     <row r="220">
       <c r="A220" s="1"/>
@@ -9460,6 +10205,8 @@
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
+      <c r="X220" s="1"/>
+      <c r="Y220" s="1"/>
     </row>
     <row r="221">
       <c r="A221" s="1"/>
@@ -9485,6 +10232,8 @@
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
       <c r="W221" s="1"/>
+      <c r="X221" s="1"/>
+      <c r="Y221" s="1"/>
     </row>
     <row r="222">
       <c r="A222" s="1"/>
@@ -9510,6 +10259,8 @@
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
+      <c r="X222" s="1"/>
+      <c r="Y222" s="1"/>
     </row>
     <row r="223">
       <c r="A223" s="1"/>
@@ -9535,6 +10286,8 @@
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
       <c r="W223" s="1"/>
+      <c r="X223" s="1"/>
+      <c r="Y223" s="1"/>
     </row>
     <row r="224">
       <c r="A224" s="1"/>
@@ -9560,6 +10313,8 @@
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
       <c r="W224" s="1"/>
+      <c r="X224" s="1"/>
+      <c r="Y224" s="1"/>
     </row>
     <row r="225">
       <c r="A225" s="1"/>
@@ -9585,6 +10340,8 @@
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
+      <c r="X225" s="1"/>
+      <c r="Y225" s="1"/>
     </row>
     <row r="226">
       <c r="A226" s="1"/>
@@ -9610,6 +10367,8 @@
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
       <c r="W226" s="1"/>
+      <c r="X226" s="1"/>
+      <c r="Y226" s="1"/>
     </row>
     <row r="227">
       <c r="A227" s="1"/>
@@ -9635,6 +10394,8 @@
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
       <c r="W227" s="1"/>
+      <c r="X227" s="1"/>
+      <c r="Y227" s="1"/>
     </row>
     <row r="228">
       <c r="A228" s="1"/>
@@ -9660,6 +10421,8 @@
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
       <c r="W228" s="1"/>
+      <c r="X228" s="1"/>
+      <c r="Y228" s="1"/>
     </row>
     <row r="229">
       <c r="A229" s="1"/>
@@ -9685,6 +10448,8 @@
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
+      <c r="X229" s="1"/>
+      <c r="Y229" s="1"/>
     </row>
     <row r="230">
       <c r="A230" s="1"/>
@@ -9710,6 +10475,8 @@
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
       <c r="W230" s="1"/>
+      <c r="X230" s="1"/>
+      <c r="Y230" s="1"/>
     </row>
     <row r="231">
       <c r="A231" s="1"/>
@@ -9735,6 +10502,8 @@
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
       <c r="W231" s="1"/>
+      <c r="X231" s="1"/>
+      <c r="Y231" s="1"/>
     </row>
     <row r="232">
       <c r="A232" s="1"/>
@@ -9760,6 +10529,8 @@
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
       <c r="W232" s="1"/>
+      <c r="X232" s="1"/>
+      <c r="Y232" s="1"/>
     </row>
     <row r="233">
       <c r="A233" s="1"/>
@@ -9785,6 +10556,8 @@
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
       <c r="W233" s="1"/>
+      <c r="X233" s="1"/>
+      <c r="Y233" s="1"/>
     </row>
     <row r="234">
       <c r="A234" s="1"/>
@@ -9810,6 +10583,8 @@
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
       <c r="W234" s="1"/>
+      <c r="X234" s="1"/>
+      <c r="Y234" s="1"/>
     </row>
     <row r="235">
       <c r="A235" s="1"/>
@@ -9835,6 +10610,8 @@
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
       <c r="W235" s="1"/>
+      <c r="X235" s="1"/>
+      <c r="Y235" s="1"/>
     </row>
     <row r="236">
       <c r="A236" s="1"/>
@@ -9860,6 +10637,8 @@
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
       <c r="W236" s="1"/>
+      <c r="X236" s="1"/>
+      <c r="Y236" s="1"/>
     </row>
     <row r="237">
       <c r="A237" s="1"/>
@@ -9885,6 +10664,8 @@
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
       <c r="W237" s="1"/>
+      <c r="X237" s="1"/>
+      <c r="Y237" s="1"/>
     </row>
     <row r="238">
       <c r="A238" s="1"/>
@@ -9910,6 +10691,8 @@
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
       <c r="W238" s="1"/>
+      <c r="X238" s="1"/>
+      <c r="Y238" s="1"/>
     </row>
     <row r="239">
       <c r="A239" s="1"/>
@@ -9935,6 +10718,8 @@
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
       <c r="W239" s="1"/>
+      <c r="X239" s="1"/>
+      <c r="Y239" s="1"/>
     </row>
     <row r="240">
       <c r="A240" s="1"/>
@@ -9960,6 +10745,8 @@
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
       <c r="W240" s="1"/>
+      <c r="X240" s="1"/>
+      <c r="Y240" s="1"/>
     </row>
     <row r="241">
       <c r="A241" s="1"/>
@@ -9985,6 +10772,8 @@
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
       <c r="W241" s="1"/>
+      <c r="X241" s="1"/>
+      <c r="Y241" s="1"/>
     </row>
     <row r="242">
       <c r="A242" s="1"/>
@@ -10010,6 +10799,8 @@
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
       <c r="W242" s="1"/>
+      <c r="X242" s="1"/>
+      <c r="Y242" s="1"/>
     </row>
     <row r="243">
       <c r="A243" s="1"/>
@@ -10035,6 +10826,8 @@
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
       <c r="W243" s="1"/>
+      <c r="X243" s="1"/>
+      <c r="Y243" s="1"/>
     </row>
     <row r="244">
       <c r="A244" s="1"/>
@@ -10060,6 +10853,8 @@
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
       <c r="W244" s="1"/>
+      <c r="X244" s="1"/>
+      <c r="Y244" s="1"/>
     </row>
     <row r="245">
       <c r="A245" s="1"/>
@@ -10085,6 +10880,8 @@
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
       <c r="W245" s="1"/>
+      <c r="X245" s="1"/>
+      <c r="Y245" s="1"/>
     </row>
     <row r="246">
       <c r="A246" s="1"/>
@@ -10110,6 +10907,8 @@
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
+      <c r="X246" s="1"/>
+      <c r="Y246" s="1"/>
     </row>
     <row r="247">
       <c r="A247" s="1"/>
@@ -10135,6 +10934,8 @@
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
+      <c r="X247" s="1"/>
+      <c r="Y247" s="1"/>
     </row>
     <row r="248">
       <c r="A248" s="1"/>
@@ -10160,6 +10961,8 @@
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
+      <c r="X248" s="1"/>
+      <c r="Y248" s="1"/>
     </row>
     <row r="249">
       <c r="A249" s="1"/>
@@ -10185,6 +10988,8 @@
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
       <c r="W249" s="1"/>
+      <c r="X249" s="1"/>
+      <c r="Y249" s="1"/>
     </row>
     <row r="250">
       <c r="A250" s="1"/>
@@ -10210,6 +11015,8 @@
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
       <c r="W250" s="1"/>
+      <c r="X250" s="1"/>
+      <c r="Y250" s="1"/>
     </row>
     <row r="251">
       <c r="A251" s="1"/>
@@ -10235,6 +11042,8 @@
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
       <c r="W251" s="1"/>
+      <c r="X251" s="1"/>
+      <c r="Y251" s="1"/>
     </row>
     <row r="252">
       <c r="A252" s="1"/>
@@ -10260,6 +11069,8 @@
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
       <c r="W252" s="1"/>
+      <c r="X252" s="1"/>
+      <c r="Y252" s="1"/>
     </row>
     <row r="253">
       <c r="A253" s="1"/>
@@ -10285,6 +11096,8 @@
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
       <c r="W253" s="1"/>
+      <c r="X253" s="1"/>
+      <c r="Y253" s="1"/>
     </row>
     <row r="254">
       <c r="A254" s="1"/>
@@ -10310,6 +11123,8 @@
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
       <c r="W254" s="1"/>
+      <c r="X254" s="1"/>
+      <c r="Y254" s="1"/>
     </row>
     <row r="255">
       <c r="A255" s="1"/>
@@ -10335,6 +11150,8 @@
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
       <c r="W255" s="1"/>
+      <c r="X255" s="1"/>
+      <c r="Y255" s="1"/>
     </row>
     <row r="256">
       <c r="A256" s="1"/>
@@ -10360,6 +11177,8 @@
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
       <c r="W256" s="1"/>
+      <c r="X256" s="1"/>
+      <c r="Y256" s="1"/>
     </row>
     <row r="257">
       <c r="A257" s="1"/>
@@ -10385,6 +11204,8 @@
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
       <c r="W257" s="1"/>
+      <c r="X257" s="1"/>
+      <c r="Y257" s="1"/>
     </row>
     <row r="258">
       <c r="A258" s="1"/>
@@ -10410,6 +11231,8 @@
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
       <c r="W258" s="1"/>
+      <c r="X258" s="1"/>
+      <c r="Y258" s="1"/>
     </row>
     <row r="259">
       <c r="A259" s="1"/>
@@ -10435,6 +11258,8 @@
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
       <c r="W259" s="1"/>
+      <c r="X259" s="1"/>
+      <c r="Y259" s="1"/>
     </row>
     <row r="260">
       <c r="A260" s="1"/>
@@ -10460,6 +11285,8 @@
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
       <c r="W260" s="1"/>
+      <c r="X260" s="1"/>
+      <c r="Y260" s="1"/>
     </row>
     <row r="261">
       <c r="A261" s="1"/>
@@ -10485,6 +11312,8 @@
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
       <c r="W261" s="1"/>
+      <c r="X261" s="1"/>
+      <c r="Y261" s="1"/>
     </row>
     <row r="262">
       <c r="A262" s="1"/>
@@ -10510,6 +11339,8 @@
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
       <c r="W262" s="1"/>
+      <c r="X262" s="1"/>
+      <c r="Y262" s="1"/>
     </row>
     <row r="263">
       <c r="A263" s="1"/>
@@ -10535,6 +11366,8 @@
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
       <c r="W263" s="1"/>
+      <c r="X263" s="1"/>
+      <c r="Y263" s="1"/>
     </row>
     <row r="264">
       <c r="A264" s="1"/>
@@ -10560,6 +11393,8 @@
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
       <c r="W264" s="1"/>
+      <c r="X264" s="1"/>
+      <c r="Y264" s="1"/>
     </row>
     <row r="265">
       <c r="A265" s="1"/>
@@ -10585,6 +11420,8 @@
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
       <c r="W265" s="1"/>
+      <c r="X265" s="1"/>
+      <c r="Y265" s="1"/>
     </row>
     <row r="266">
       <c r="A266" s="1"/>
@@ -10610,6 +11447,8 @@
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
       <c r="W266" s="1"/>
+      <c r="X266" s="1"/>
+      <c r="Y266" s="1"/>
     </row>
     <row r="267">
       <c r="A267" s="1"/>
@@ -10635,6 +11474,8 @@
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
       <c r="W267" s="1"/>
+      <c r="X267" s="1"/>
+      <c r="Y267" s="1"/>
     </row>
     <row r="268">
       <c r="A268" s="1"/>
@@ -10660,6 +11501,8 @@
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
       <c r="W268" s="1"/>
+      <c r="X268" s="1"/>
+      <c r="Y268" s="1"/>
     </row>
     <row r="269">
       <c r="A269" s="1"/>
@@ -10685,6 +11528,8 @@
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
       <c r="W269" s="1"/>
+      <c r="X269" s="1"/>
+      <c r="Y269" s="1"/>
     </row>
     <row r="270">
       <c r="A270" s="1"/>
@@ -10710,6 +11555,8 @@
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
       <c r="W270" s="1"/>
+      <c r="X270" s="1"/>
+      <c r="Y270" s="1"/>
     </row>
     <row r="271">
       <c r="A271" s="1"/>
@@ -10735,6 +11582,8 @@
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
       <c r="W271" s="1"/>
+      <c r="X271" s="1"/>
+      <c r="Y271" s="1"/>
     </row>
     <row r="272">
       <c r="A272" s="1"/>
@@ -10760,6 +11609,8 @@
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
       <c r="W272" s="1"/>
+      <c r="X272" s="1"/>
+      <c r="Y272" s="1"/>
     </row>
     <row r="273">
       <c r="A273" s="1"/>
@@ -10785,6 +11636,8 @@
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
       <c r="W273" s="1"/>
+      <c r="X273" s="1"/>
+      <c r="Y273" s="1"/>
     </row>
     <row r="274">
       <c r="A274" s="1"/>
@@ -10810,9 +11663,11 @@
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
       <c r="W274" s="1"/>
+      <c r="X274" s="1"/>
+      <c r="Y274" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W74"/>
+  <autoFilter ref="A1:Y74"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/data/raw/Democracy in Action/review/dia_2008_labor_review.xlsx
+++ b/data/raw/Democracy in Action/review/dia_2008_labor_review.xlsx
@@ -1,1231 +1,1325 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/katherineparslow/Documents/repos/presidential-endorsements/data/raw/Democracy in Action/review/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DA0CF2-26DB-C742-B62E-C7C2B92F2496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="review" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="review" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'review'!$A$1:$Y$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">review!$A$1:$Y$74</definedName>
   </definedNames>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="400">
-  <si>
-    <t xml:space="preserve">row_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">review_action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">review_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contest_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">party</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorsee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorser_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorser_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorser_party_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">district</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_raw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">record_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">switch_direction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">switch_candidate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evidence_url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parsed_ok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw_text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">section_heading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorsee_mention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org_info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">all_dates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">2008D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hillary Clinton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operative Plasterers' and Cement Masons' International Association (OPCMIA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Labor Organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">April 16, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endorsement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">clinton041608opcmia.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operative Plasterers' and Cement Masons' International Association (OPCMIA) Organization: General President Patrick D. Finley, General Secretary-Treasurer Earl F. Hurd, Exec. Vice-President Daniel E. Stepano, four Vice Presidents. OPCMIA announced its endorsement of Sen. Clinton on April 16, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLINTON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: General President Patrick D. Finley, General Secretary-Treasurer Earl F. Hurd, Exec. Vice-President Daniel E. Stepano, four Vice Presidents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Farm Workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 22, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/ufw012208pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Farm Workers Organization: President Arturo Rodriguez. Note that United Farm Workers is a Change to Win affiliate. Represents more than 27,000 farm workers. Announced endorsement of Sen. Clinton on Jan. 22, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: President Arturo Rodriguez. Note that United Farm Workers is a Change to Win affiliate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Union of Painters and Allied Trades (IUPAT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 19, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/iupat121907pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Union of Painters and Allied Trades (IUPAT) Organization: General Executive Board consists of General President/Director of Organizing James A. Williams, Executive General Vice President Kenneth E. Rigmaiden, General Secretary-Treasurer George Galis, four General Vice Presidents, and General President Emeritus Mike Monroe. Represents 160,000 active and retired members in the finishing trades. Announced endorsement of Sen. Clinton on Dec. 19, 2007.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: General Executive Board consists of General President/Director of Organizing James A. Williams, Executive General Vice President Kenneth E. Rigmaiden, General Secretary-Treasurer George Galis, four General Vice Presidents, and General President Emeritus Mike Monroe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Alliance of Theatrical Stage Employes, Moving Picture Technicians, Artists and Allied Crafts (IATSE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 11, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/clinton/clinton121107iatse.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Alliance of Theatrical Stage Employes, Moving Picture Technicians, Artists and Allied Crafts (IATSE) Organization: International President Thomas C. Short and General Secretary-Treasurer James B. Wood head up the 17-person General Executive Board.. Represents more than 100,000 members in the motion picture, theatrical and television professions. Announced endorsement of Sen Clinton on Dec. 11, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: International President Thomas C. Short and General Secretary-Treasurer James B. Wood head up the 17-person General Executive Board..</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Office and Professional Employees International Union (OPEIU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 3, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/clinton120307opeiu.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Office and Professional Employees International Union (OPEIU) Organization: International President Michael Goodwin; Secretary-Treasurer Nancy Wohlforth. Represents more than 125,000 members in the professional, technical and administrative fields. Announced endorsement of Sen. Clinton on Dec. 3, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: International President Michael Goodwin; Secretary-Treasurer Nancy Wohlforth.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amalgamated Transit Union (ATU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nov. 29, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/atu112907pr.html; http://p2008.org/labor/clinton112907atu.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amalgamated Transit Union (ATU) Organization: International President Warren S. George; International Executive Vice President Michael Siano; International Secretary-Treasurer Oscar Owens. 267 locals throughout the U.S. and Canada. "The largest labor organization representing transit workers in the United States and Canada," ATU claims over 180,000 members in the U.S. and Canada. Announced endorsement of Sen. Clinton on Nov. 29, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: International President Warren S. George; International Executive Vice President Michael Siano; International Secretary-Treasurer Oscar Owens. 267 locals throughout the U.S. and Canada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheet Metal Workers International Association (SMWIA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nov. 17, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/smwia111707pr.html; http://p2008.org/labor/clinton111707smwia.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheet Metal Workers International Association (SMWIA) Organization: General President Michael J. Sullivan, General Secretary - Treasurer Joseph J. Nigro, 11 General Vice Presidents. Note: SMWIA is in the process of merging with the United Transportation Union (UTU) to form the International Association of Sheet Metal, Air, Rail and Transportation Workers (SMART); the merger will take effect Jan. 1, 2008. Announced endorsement of Sen. Clinton on Nov. 17, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: General President Michael J. Sullivan, General Secretary - Treasurer Joseph J. Nigro, 11 General Vice Presidents. Note: SMWIA is in the process of merging with the United Transportation Union (UTU) to form the International Association of Sheet Metal, Air, Rail and Transportation Workers (SMART); the merger will take effect Jan. 1, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of State, County and Municipal Employees (AFSCME)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oct. 31, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/clinton/clinton103107afscme.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of State, County and Municipal Employees (AFSCME) Organization: President Gerald W. McEntee, Secretary-Treasurer William Lucy, Executive Board (International Vice Presidents). More than 3,500 local unions in 46 states, the District of Columbia and Puerto Rico; 61 Councils. "The largest union for workers in the public service with 1.4 million members nationwide...represents a diverse group of service and health care workers in the public and private sectors including nurses, EMTs, bus drivers, child care providers, custodians and librarians." Announced endorsement of Sen. Clinton on Oct. 31, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: President Gerald W. McEntee, Secretary-Treasurer William Lucy, Executive Board (International Vice Presidents). More than 3,500 local unions in 46 states, the District of Columbia and Puerto Rico; 61 Councils.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of Teachers (AFT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oct. 3, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/aft100307pr.html; http://p2008.org/clinton/clinton100307aft.html; http://p2008.org/photos07/photo100307.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of Teachers (AFT) Organization: 41 member executive council. President Edward J. McElroy; Secretary-Treasurer Nat LaCour; Executive Vice President Antonia Cortese. AFT's more than 1.4 million members include pre-K through 12th grade teachers; paraprofessionals and school-related personnel (PSRP); local, state and federal employees; higher education faculty and staff; and nurses and other healthcare professionals. The union also includes more than 170,000 retiree members. More than 3,000 local affiliates nationwide; 43 state affiliates. Announced endorsement of Sen. Clinton on Oct. 3, 2007. campaign, see also photos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: 41 member executive council. President Edward J. McElroy; Secretary-Treasurer Nat LaCour; Executive Vice President Antonia Cortese.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Union of Bricklayers and Allied Craftworkers (BAC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sept. 24, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/clinton092407bac.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Union of Bricklayers and Allied Craftworkers (BAC) Organization: Executive Board comprises President John J. Flynn, Secretary-Treasurer James Boland and Executive Vice Presidents Ken Lambert, Gerald O’Malley and Gerard Scarano. Executive Council, the Union's highest advisory body, is made up of the Executive Board, Regional Vice Presidents from BAC's five Regions in the U.S. and Canada, IU Regional Directors, the Canadian Co-Chair, Craft Vice Presidents, and At-Large Members. Represents roughly 100,000 skilled masonry-trowel trades craftworkers. Announced endorsement of Sen. Clinton on Sept. 24, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: Executive Board comprises President John J. Flynn, Secretary-Treasurer James Boland and Executive Vice Presidents Ken Lambert, Gerald O’Malley and Gerard Scarano. Executive Council, the Union's highest advisory body, is made up of the Executive Board, Regional Vice Presidents from BAC's five Regions in the U.S. and Canada, IU Regional Directors, the Canadian Co-Chair, Craft Vice Presidents, and At-Large Members.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Association of Letter Carriers (NALC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sept. 12, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/nalc091207pr.html; http://p2008.org/labor/clinton091207nalc.html; http://p2008.org/photos07/photo091207.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Association of Letter Carriers (NALC) Organization: 28-member Executive Council (10 Resident National officers, 3 National Trustees and 15 National Business Agents) headed by National President William H. “Bill” Young. Represents about 300,00 active and retired members, of which a bit more than two-thirds are active city delivery letter carriers employed by the U.S. Postal Service. 2,500 local branches. Announced endorsement of Sen. Clinton on Sept. 12, 2007. campaign, see also photos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: 28-member Executive Council (10 Resident National officers, 3 National Trustees and 15 National Business Agents) headed by National President William H. “Bill” Young.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Association of Machinists and Aerospace Workers (IAM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aug. 30, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/iam083007endorse.html; http://p2008.org/labor/clinton083007iam.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Association of Machinists and Aerospace Workers (IAM) Organization: The Executive Council consists of International President R. Thomas Buffenbarger, General Secretary-Treasurer Warren L. Mart, and 7 General Vice Presidents. Represents 730,000 members across North America including aerospace, automotive, government employees, transportation, and woodworkers. Dual endorsement of Sen. Clinton and former Gov. Huckabee announced on Aug. 30, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: The Executive Council consists of International President R. Thomas Buffenbarger, General Secretary-Treasurer Warren L. Mart, and 7 General Vice Presidents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transportation Communications Union (TCU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">split from the International Association of Machinists and Aerospace Workers (IAM) cell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.goiam.org/tcunion.cfm; http://p2008.org/labor/tcu083007pr.html; http://p2008.org/labor/clinton090607tcu.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Association of Machinists and Aerospace Workers (IAM) Additionally, the Transportation Communications Union (TCU), an IAM affiliate headquartered in Rockville, MD with 65,000 active and retired members ("approximately 46,000 members in the U.S., most employed in the railroad industry") announced its endorsement of Sen. Clinton on Aug. 30, 2007. [TCU affiliated with the IAM in July 2005, and a full merger is to occur no later than January 2012]. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aug. 30, 2007; July 2005; January 2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Transportation Union (UTU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aug. 28, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/utu082807endorse.html; http://p2008.org/labor/clinton082807utu.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Transportation Union (UTU) Organization: International President Paul Thompson (retiring Dec. 31). Cleveland, Ohio-based transportation labor union representing about 125,000 active and retired railroad, bus and mass transit workers in the United States and Canada. Announced endorsement of Sen. Clinton announced on Aug. 28, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: International President Paul Thompson (retiring Dec. 31).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retail, Wholesale and Department Store Union (RWDSU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://www.rwdsu.info/en/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Retail, Wholesale and Department Store Union (RWDSU), a UFCW affiliate representing 100,000 workers in the U.S. and Canada, is backing Sen. Clinton; the Executive Board voted unanimously to support Sen. Clinton at a meeting in May 2007. (Clinton addressed the RWDSU Executive Board on May 11, 2007. In 1999 the union was the first to endorse her campaign for Senate).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May 2007; May 11, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barack Obama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Mine Workers of America (UMWA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May 21, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">from</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/umwa052108pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Mine Workers of America (UMWA) Organization: President Cecil Roberts and Secretary-Treasurer Dan Kane. Originally endorsed Sen. Edwards in Sept. 2007. Represents 105,000 active and retired coal miners, municipal employees, health care workers and manufacturing workers in North America. UMWA announced its endorsemet of Sen. Obama on May 21, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: President Cecil Roberts and Secretary-Treasurer Dan Kane.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sept. 2007; May 21, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Steelworkers (USW)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May 15, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">usw051508pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Steelworkers (USW) Organization: International President Leo W. Gerard and International Secretary-Treasurer James D. English head up the International Executive Board. Originally endorsed Sen. Edwards in Sept. 2007. Represents 1.2 million members and retirees ("the largest industrial union in North America"). United Steelworkers announced its endorsement of Sen. Obama on May 15, 2008, the day after Edwards endorsed Obama.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: International President Leo W. Gerard and International Secretary-Treasurer James D. English head up the International Executive Board.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sept. 2007; May 15, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of Government Employees</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May 9, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">afge050908pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Federation of Government Employees Organization: National President John Gage. The largest federal employee union representing 600,000 federal and D.C. government workers nationwide and overseas. Announced endorsement of Sen. Obama on May 9, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: National President John Gage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change to Win</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 21, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/changetowin022108pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change to Win Organization: 7 affiliated unions. Chair Anna Berger. Announced endorsement of Sen. Obama on Feb. 21, 2008. Carpenters, LIUNA and UFW abstained.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: 7 affiliated unions. Chair Anna Berger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Brotherhood of Teamsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 20, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/teamsters022008pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Brotherhood of Teamsters Organization: General President James P. Hoffa; General Secretary-Treasurer Tom Keegel; General Executive Board consisting of 22 Vice Presidents. Represents 1.4 million workers who work in areas including warehouse, parcel, freight, public employees and industrial trades. Announced endorsement of Sen. Obama on Feb. 20, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: General President James P. Hoffa; General Secretary-Treasurer Tom Keegel; General Executive Board consisting of 22 Vice Presidents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Brotherhood of Boilermakers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/boilermakers022008pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Brotherhood of Boilermakers Organization: International President Newton B. Jones; International Secretary-Treasurer William T. Creeden; five International Vice Presidents. Headquartered in Kansas City, KS, the International Brotherhood of Boilermakers, Iron Ship Builders, Blacksmiths, Forgers and Helpers, AFL-CIO represents 65,000 members. Announced endorsement of Sen. Obama on Feb. 20, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: International President Newton B. Jones; International Secretary-Treasurer William T. Creeden; five International Vice Presidents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Employees International Union (SEIU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 15, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/seiu100807pr.html; http://p2008.org/photos07/seiu0907/seiu0907main.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Employees International Union (SEIU) Organization: President Andy Stern, Secretary-Treasurer Anna Burger; Executive Vice Presidents Mary Kay Henry, Gerry Hudson, Eliseo Medina, andTom Woodruff. SEIU represents 1.9 million members and and 50,000 retirees in the United States, Canada, and Puerto Rico focused in hospital systems and long term care (900,000 members), property services (225,000 members), and public services (850,000 members). On Oct. 8, 2007 the SEIU announced that its local unions would decide on presidential primary endorsements on a state-by-state basis, with decisions announced no earlier than Oct. 15, 2007. Local unions did endorse, opting for Edwards (CA, ID, IA, MI, MT, MN, OH, OR, WA, WV; MA; NH), Obama (IL, MO-KS, WI) and Clinton (SEIU Locals 1199 and 32BJ). On Feb. 15, 2008 in a conference call the SEIU executive board endorsed Sen. Obama. see also photos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: President Andy Stern, Secretary-Treasurer Anna Burger; Executive Vice Presidents Mary Kay Henry, Gerry Hudson, Eliseo Medina, andTom Woodruff.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oct. 8, 2007; Oct. 15, 2007; Feb. 15, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Food and Commercial Workers Union (UFCW)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 14, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/ufcw021408pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Food and Commercial Workers Union (UFCW) Organization: International President Joseph T. Hansen; International Secretary-Treasurer Anthony M. Perrone; Executive Vice Presidents William T. McDonough, Patrick J. O'Neill, and Wayne E. Hanley. Represents more than 1.3 million workers, primarily in the retail and meatpacking, food processing and poultry industries. Announced endorsement of Sen. Obama on Feb. 14, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: International President Joseph T. Hansen; International Secretary-Treasurer Anthony M. Perrone; Executive Vice Presidents William T. McDonough, Patrick J. O'Neill, and Wayne E. Hanley.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport Workers Union (TWU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 1, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/twu020108pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport Workers Union (TWU) Organization: International President James C. Little. Originally endorsed Sen. Edwards in Sept. 2007. Represents 200,000 active and retired members. Announced endorsement of Sen. Obama on Feb. 1, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: International President James C. Little.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sept. 2007; Feb. 1, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNITE HERE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan. 9, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/unitehere010908pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNITE HERE Organization: General President Bruce Raynor. President, Hospitality Industry John W. Wilhelm. Represents nearly half a million workers in the hospitality, gaming, apparel, textile, retail, distribution, food service and laundry industries in North America. Held its founding convention July 9, 2004. Announced endorsement of Sen. Obama on Jan. 9, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: General President Bruce Raynor. President, Hospitality Industry John W. Wilhelm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">July 9, 2004; Jan. 9, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Association (UA - Plumbers and Pipe Fitters)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/ua010908pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Association (UA - Plumbers and Pipe Fitters) Organization: International President William P. Hite, General Secretary-Treasurer Patrick R. Perno. Represents approximately 340,000 members who belong to over 300 individual local unions across North America. Announced endorsement of Sen. Obama on Jan. 9, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: International President William P. Hite, General Secretary-Treasurer Patrick R. Perno.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Dodd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Association of Fire Fighters (IAFF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aug. 29, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/iaff082907pr.html; http://p2008.org/labor/iaff082907endorse.html; http://p2008.org/labor/dodd082907iaff.html; http://p2008.org/interestg08/iaff050807pr.html; http://p2008.org/iaff031407/iaff0307main.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Association of Fire Fighters (IAFF) Organization: The Executive Board is chaired by General President Harold A. Schaitberger and includes Secretary-Treasurer Vinnie Bollon and 16 regional Vice Presidents. Represents more than 281,000 full-time professional fire fighters and paramedics. More than 3,100 affiliates and their members protect communities in every state in the United States and in Canada. Announced (2) endorsement of Sen. Dodd on Aug. 29, 2007. campaign -May 10-11, 2007...IAFF Federation of State and Provincial Professional Fire Fighters meeting in Portsmouth, NH (press release). -March 14, 2007..."IAFF Bipartisan 2008 Presidential Forum" during International Association of Fire Fighters (IAFF) Legislative Conference in Washington, DC. -The Jan.-Feb. 2007 issue of International Fire Fighter contained a message from IAFF General President Harold A. Schaitberger outlining endorsement criteria.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DODD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization: The Executive Board is chaired by General President Harold A. Schaitberger and includes Secretary-Treasurer Vinnie Bollon and 16 regional Vice Presidents.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aug. 29, 2007; March 14, 2007; Feb. 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sept. 6, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/twu090607pr.html; http://p2008.org/labor/edwards090607twu.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport Workers Union (TWU) Organization: International President James C. Little. Represents 200,000 active and retired members. Announced endorsement of former Sen. Edwards on Sept. 6, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDWARDS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sept. 3, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/usw090307pr.html; http://p2008.org/labor/edwards090307usw.html; http://p2008.org/interestg08/usw070207pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Steelworkers (USW) Organization: International President Leo W. Gerard and International Secretary-Treasurer James D. English head up the International Executive Board. Represents 1.2 million members and retirees ("the largest industrial union in North America"). Announced endorsement of former Sen. Edwards on Sept. 3, 2007. campaign -July 5-6, 2007...Four Democratic candidates spoke at the United Steelworkers (USW) Presidential Candidates' Forum on Renewing American Manufacturing at Crowne Plaza Cleveland City Centre Hotel in Cleveland, OH.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/edwards090307usw.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Mine Workers of America (UMWA) Organization: President Cecil Roberts and Secretary-Treasurer Dan Kane. Represents 105,000 active and retired coal miners, municipal employees, health care workers and manufacturing workers in North America. Announced endorsement of former Sen. Edwards on Sept. 3, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Brotherhood of Carpenters and Joiners of America (UBC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/carpenters083007pr.html; http://p2008.org/labor/edwards083007carp.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Brotherhood of Carpenters and Joiners of America (UBC) Represents more than 520,000 men and women throughout the building-trades industries including carpenters, cabinetmakers, millwrights, piledrivers, lathers, framers, floorlayers, roofers, drywallers, and workers in forest-products and related industries. Announced endorsement of former Sen. Edwards on Aug. 30, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mike Huckabee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/iam083007endorse.html; http://p2008.org/labor/huck083007iam.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Association of Machinists and Aerospace Workers (IAM) Organization: The Executive Council consists of International President R. Thomas Buffenbarger, General Secretary-Treasurer Warren L. Mart, and 7 General Vice Presidents. Represents 730,000 members across North America including aerospace, automotive, government employees, transportation, and woodworkers. Announced dual endorsement of Sen. Clinton and former Gov. Huckabee on Aug. 30, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUCKABEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Biden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delaware Plumbers &amp; Pipefitters Local Union 74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State/Local Labor Organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 21, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sen. Joe Biden received the endorsement of Delaware Plumbers &amp; Pipefitters Local Union 74 on Dec. 21, 2007. Business Manager is John J. Czerwinski.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State/Local</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIDEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sen. Joe Biden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Auto Workers (UAW) Delaware State CAP Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 18, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/biden/biden121807pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sen. Joe Biden received the endorsement of the United Auto Workers (UAW) Delaware State CAP Council on Dec. 18, 2007. There are over 5,000 active and 7,000 retired members in Delaware; CAP Council President is Richard McDonaugh, Jr.. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delaware Communications Workers of America (CWA), Local 13101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 17, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sen. Joe Biden received the endorsement of the Delaware Communications Workers of America (CWA), Local 13101 on Dec. 17, 2007. CWA Local 13101 Executive President is Bud Speakman.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plumbing, Pipefitting, and Refrigeration Workers UA Local 525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 14, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/biden/biden121407prnv.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Plumbing, Pipefitting, and Refrigeration Workers UA Local 525 [Nevada] endorsed Sen. Joe Biden on Dec. 14, 2007. Business Manager is Brett McCoy. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delaware State Education Association (DSEA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oct. 18, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/biden/biden101807dsea.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Biden campaign announced the endorsement of the 11,000 member Delaware State Education Association (DSEA) on Oct. 18, 2007. DSEA is the state affiliate of the 2.6 million member National Education Association. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delaware State AFL-CIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">June 14, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Delaware State AFL-CIO announced its unanimous endorsement of Sen. Joe Biden for president on June 14, 2007.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Local 1199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">announced together in one paragraph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Clinton campaign announced the endorsements of SEIU Locals 1199 and 32BJ on Dec. 14, 2007. "SEIU 1199 is the largest and fastest growing health care union in the country, with more than 300,000 members in Massachusetts, Maryland, New York and Washington, DC... SEIU 32BJ is the largest property service workers union in the country with more than 100,000 members in New York, New Jersey, Connecticut, Pennsylvania, Maryland, Virginia and Washington, DC."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clinton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Local 32BJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEA-NH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 6, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/clinton120607prnh.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEA-NH announced its endorsement of Sen. Hillary Clinton on Dec. 6, 2007. NEA-NH is the largest union in New Hampshire with 16,000 members. President is Rhonda Wesolowski. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sen. Hillary Clinton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IATSE Stage Employees Local 720 in Las Vegas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/clinton/clinton112907prnv.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IATSE Stage Employees Local 720 in Las Vegas announced its endorsement of Sen. Hillary Clinton on Nov. 29, 2007. Local 720 includes approximately 4,500 members and affiliated workers involved with the convention and trade show industry, theatrical productions and live entertainment events in southern Nevada. Local 720 President is Hal Ritzer. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSEA Local 1000 AFSCME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">July 25, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSEA Local 1000 AFSCME, which bills itself as "New York's leading union" and claims 265,000 members, announced its endorsement of Sen. Hillary Clinton on July 25, 2007.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UFCW Local 1500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">June 21, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Clinton exploratory committee announced the endorsement of UFCW Local 1500 (represents more than 22,000 members working in the grocery industry across the metropolitan New York area; President Bruce Both) on June 21, 2007.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Union of Operating Engineers Local 324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">June 15, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Clinton exploratory committee announced the endorsement of Michigan-based International Union of Operating Engineers Local 324 on June 15, 2007.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communications Workers of America in Nevada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/edw120607prcwa.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communications Workers of America in Nevada announced its endorsement of Sen. John Edwards on Dec. 6, 2007; CWA Local 9413 President is Chuck Benway and Executive Vice President is Liz Sorenson. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sen. John Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iowa Postal Workers Union</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/edwards/edw101807pripwu.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Edwards campaign announced the endorsement of the Iowa Postal Workers Union, representing more than 3,000 workers in all 99 counties, on Oct. 18, 2007. The Iowa Postal Workers Union is the statewide branch of the AFL-CIO-affiliated American Postal Workers Union. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Hampshire State Employees' Association (SEIU local 1984)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/edwards/edwards103107nhsea.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The New Hampshire State Employees' Association (SEIU local 1984) announced its endorsement of Sen. John Edwards on Oct. 31, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massachusetts Council of the Service Employees International Union</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Massachusetts Council of the Service Employees International Union (90,000 members) announced its endorsement of Sen. John Edwards on Oct. 18, 2007.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU California State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oct. 15, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">656,000 members; one of ten SEIU state councils announced together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/edw101507pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten SEIU State Councils announced their endorsement of Sen. John Edwards on Oct. 15, 2007. California (656,000 members), Idaho (450 members), Iowa (2,000 members), Michigan (70,000 members), Montana (500 members), Minnesota (28,000 members), Ohio (22,000 members), Oregon (46,000 members), Washington (103,000 members) and West Virginia (4,000 members). campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Idaho State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450 members; one of ten SEIU state councils announced together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Iowa State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,000 members; one of ten SEIU state councils announced together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Michigan State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70,000 members; one of ten SEIU state councils announced together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Montana State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500 members; one of ten SEIU state councils announced together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Minnesota State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28,000 members; one of ten SEIU state councils announced together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Ohio State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,000 members; one of ten SEIU state councils announced together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Oregon State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46,000 members; one of ten SEIU state councils announced together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Washington State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103,000 members; one of ten SEIU state councils announced together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU West Virginia State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,000 members; one of ten SEIU state councils announced together</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oregon AFSCME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March 15, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/orafscme031508.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oregon AFSCME announced its endorsement of Sen. Barack Obama on March 15, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sen. Barack Obama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oregon Education Association</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March 8, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Oregon Education Association announced its endorsement of Sen. Barack Obama on March 8, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Council of Social Security Field Office Locals, Council 220 AFGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 29, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/afge220022908pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Council of Social Security Field Office Locals, Council 220 AFGE announced its endorsement of Sen. Barack Obama on Feb. 29, 2008.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb. 5, 2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/seiuwa020508pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Washington State Council, which had endorsed Sen. John Edwards, announced its endorsement of Sen. Barack Obama on Feb. 5, 2008, four days before the Washington caucuses.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU California State Council, which had endorsed Sen. John Edwards, endorsed Sen. Barack Obama on Feb. 1, 2008, two days after Edwards announced the end of his campaign and four days before the California primary. Represents more than 650,000 members in California, including healthcare workers, nurses, janitors, librarians, homecare workers, security officers, technicians, social workers and others. Annelle Grajeda, president.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Culinary Workers Union Local 226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/obama/obama010908prnv.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Culinary Workers Union Local 226 endorsed Sen. Barack Obama on Jan. 9, 2008. The Culinary Workers Union is the largest and most politically active union in Nevada comprising 60,000 members who work at casinos on the Las Vegas Strip, downtown Las Vegas and in Reno. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Illinois Education Association-NEA (IEA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Illinois Education Association-NEA (IEA) voted to recommend Sen. Barack Obama on Dec. 6, 2007. (IEA represents more than 130,000 Illinois elementary and secondary teachers, higher education faculty and staff, educational support professionals, retired educators and college students preparing to become teachers. President is Ken Swanson).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFSCME Council 31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dec. 1, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">afscme31120107pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFSCME Council 31 announced its endorsement of Sen. Barack Obama on Dec. 1, 2007.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Auto Workers Region 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nov. 15, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/obama111507pruaw.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delegates of United Auto Workers Region 4 endorsed Sen. Barack Obama on Nov. 15, 2007. UAW Region 4 represents 64,000 active and 122,000 retirees in Iowa, Illinois, Minnesota, Wisconsin, Montana, Nebraska, North Dakota, South Dakota, and Wyoming, including 30,000 members and retirees in Iowa. Dennis Williams is director. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Wisconsin State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oct. 26, 2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Wisconsin State Council endorsed Sen. Barack Obama on Oct. 26, 2007, citing his "commitment to expanding access to affordable health care and to protecting workers' rights." (State Council President is Dian Palmer; the union has 15,000-plus members).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missouri-Kansas State Council of the Service Employees International Union</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missouri-Kansas State Council of the Service Employees International Union (represents more than 15,000 members in both states) endorsed Sen. Barack Obama on Oct. 18, 2007. Sherwin Carroll is president of the council.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Illinois State Council</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/obama101507prseiu.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEIU Illinois State Council announced its endorsement of Sen. Barack Obama on Oct. 15, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York City Correction Officers' Benevolent Association (COBA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://p2008.org/labor/obama092407pr.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The New York City Correction Officers' Benevolent Association (COBA) (represents 9,000 unionized members in New York City and is the largest municipal jail union in the country) endorsed Sen. Barack Obama on Sept. 24, 2007. campaign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bill Richardson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plasterers and Cement Masons Local 797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plasterers and Cement Masons Local 797 (represents 2,000 members in southern Nevada, business manager Marc Leavitt).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RICHARDSON</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="430">
+  <si>
+    <t>row_id</t>
+  </si>
+  <si>
+    <t>review_action</t>
+  </si>
+  <si>
+    <t>review_note</t>
+  </si>
+  <si>
+    <t>contest_id</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>party</t>
+  </si>
+  <si>
+    <t>endorsee</t>
+  </si>
+  <si>
+    <t>endorser_name</t>
+  </si>
+  <si>
+    <t>endorser_description</t>
+  </si>
+  <si>
+    <t>endorser_party_note</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>date_raw</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>record_type</t>
+  </si>
+  <si>
+    <t>switch_direction</t>
+  </si>
+  <si>
+    <t>switch_candidate</t>
+  </si>
+  <si>
+    <t>evidence_url</t>
+  </si>
+  <si>
+    <t>parsed_ok</t>
+  </si>
+  <si>
+    <t>raw_text</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>section_heading</t>
+  </si>
+  <si>
+    <t>endorsee_mention</t>
+  </si>
+  <si>
+    <t>org_info</t>
+  </si>
+  <si>
+    <t>all_dates</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2008D</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Hillary Clinton</t>
+  </si>
+  <si>
+    <t>Operative Plasterers' and Cement Masons' International Association (OPCMIA)</t>
+  </si>
+  <si>
+    <t>National Labor Organization</t>
+  </si>
+  <si>
+    <t>April 16, 2008</t>
+  </si>
+  <si>
+    <t>endorsement</t>
+  </si>
+  <si>
+    <t>clinton041608opcmia.html</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>Operative Plasterers' and Cement Masons' International Association (OPCMIA) Organization: General President Patrick D. Finley, General Secretary-Treasurer Earl F. Hurd, Exec. Vice-President Daniel E. Stepano, four Vice Presidents. OPCMIA announced its endorsement of Sen. Clinton on April 16, 2008.</t>
+  </si>
+  <si>
+    <t>National</t>
+  </si>
+  <si>
+    <t>CLINTON</t>
+  </si>
+  <si>
+    <t>Organization: General President Patrick D. Finley, General Secretary-Treasurer Earl F. Hurd, Exec. Vice-President Daniel E. Stepano, four Vice Presidents.</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>United Farm Workers</t>
+  </si>
+  <si>
+    <t>Jan. 22, 2008</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/ufw012208pr.html</t>
+  </si>
+  <si>
+    <t>United Farm Workers Organization: President Arturo Rodriguez. Note that United Farm Workers is a Change to Win affiliate. Represents more than 27,000 farm workers. Announced endorsement of Sen. Clinton on Jan. 22, 2008.</t>
+  </si>
+  <si>
+    <t>Organization: President Arturo Rodriguez. Note that United Farm Workers is a Change to Win affiliate.</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>International Union of Painters and Allied Trades (IUPAT)</t>
+  </si>
+  <si>
+    <t>Dec. 19, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/iupat121907pr.html</t>
+  </si>
+  <si>
+    <t>International Union of Painters and Allied Trades (IUPAT) Organization: General Executive Board consists of General President/Director of Organizing James A. Williams, Executive General Vice President Kenneth E. Rigmaiden, General Secretary-Treasurer George Galis, four General Vice Presidents, and General President Emeritus Mike Monroe. Represents 160,000 active and retired members in the finishing trades. Announced endorsement of Sen. Clinton on Dec. 19, 2007.</t>
+  </si>
+  <si>
+    <t>Organization: General Executive Board consists of General President/Director of Organizing James A. Williams, Executive General Vice President Kenneth E. Rigmaiden, General Secretary-Treasurer George Galis, four General Vice Presidents, and General President Emeritus Mike Monroe.</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>International Alliance of Theatrical Stage Employes, Moving Picture Technicians, Artists and Allied Crafts (IATSE)</t>
+  </si>
+  <si>
+    <t>Dec. 11, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/clinton/clinton121107iatse.html</t>
+  </si>
+  <si>
+    <t>International Alliance of Theatrical Stage Employes, Moving Picture Technicians, Artists and Allied Crafts (IATSE) Organization: International President Thomas C. Short and General Secretary-Treasurer James B. Wood head up the 17-person General Executive Board.. Represents more than 100,000 members in the motion picture, theatrical and television professions. Announced endorsement of Sen Clinton on Dec. 11, 2007. campaign</t>
+  </si>
+  <si>
+    <t>Organization: International President Thomas C. Short and General Secretary-Treasurer James B. Wood head up the 17-person General Executive Board..</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Office and Professional Employees International Union (OPEIU)</t>
+  </si>
+  <si>
+    <t>Dec. 3, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/clinton120307opeiu.html</t>
+  </si>
+  <si>
+    <t>Office and Professional Employees International Union (OPEIU) Organization: International President Michael Goodwin; Secretary-Treasurer Nancy Wohlforth. Represents more than 125,000 members in the professional, technical and administrative fields. Announced endorsement of Sen. Clinton on Dec. 3, 2007. campaign</t>
+  </si>
+  <si>
+    <t>Organization: International President Michael Goodwin; Secretary-Treasurer Nancy Wohlforth.</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Amalgamated Transit Union (ATU)</t>
+  </si>
+  <si>
+    <t>Nov. 29, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/atu112907pr.html; http://p2008.org/labor/clinton112907atu.html</t>
+  </si>
+  <si>
+    <t>Amalgamated Transit Union (ATU) Organization: International President Warren S. George; International Executive Vice President Michael Siano; International Secretary-Treasurer Oscar Owens. 267 locals throughout the U.S. and Canada. "The largest labor organization representing transit workers in the United States and Canada," ATU claims over 180,000 members in the U.S. and Canada. Announced endorsement of Sen. Clinton on Nov. 29, 2007. campaign</t>
+  </si>
+  <si>
+    <t>Organization: International President Warren S. George; International Executive Vice President Michael Siano; International Secretary-Treasurer Oscar Owens. 267 locals throughout the U.S. and Canada.</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Sheet Metal Workers International Association (SMWIA)</t>
+  </si>
+  <si>
+    <t>Nov. 17, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/smwia111707pr.html; http://p2008.org/labor/clinton111707smwia.html</t>
+  </si>
+  <si>
+    <t>Sheet Metal Workers International Association (SMWIA) Organization: General President Michael J. Sullivan, General Secretary - Treasurer Joseph J. Nigro, 11 General Vice Presidents. Note: SMWIA is in the process of merging with the United Transportation Union (UTU) to form the International Association of Sheet Metal, Air, Rail and Transportation Workers (SMART); the merger will take effect Jan. 1, 2008. Announced endorsement of Sen. Clinton on Nov. 17, 2007. campaign</t>
+  </si>
+  <si>
+    <t>Organization: General President Michael J. Sullivan, General Secretary - Treasurer Joseph J. Nigro, 11 General Vice Presidents. Note: SMWIA is in the process of merging with the United Transportation Union (UTU) to form the International Association of Sheet Metal, Air, Rail and Transportation Workers (SMART); the merger will take effect Jan. 1, 2008.</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>American Federation of State, County and Municipal Employees (AFSCME)</t>
+  </si>
+  <si>
+    <t>Oct. 31, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/clinton/clinton103107afscme.html</t>
+  </si>
+  <si>
+    <t>American Federation of State, County and Municipal Employees (AFSCME) Organization: President Gerald W. McEntee, Secretary-Treasurer William Lucy, Executive Board (International Vice Presidents). More than 3,500 local unions in 46 states, the District of Columbia and Puerto Rico; 61 Councils. "The largest union for workers in the public service with 1.4 million members nationwide...represents a diverse group of service and health care workers in the public and private sectors including nurses, EMTs, bus drivers, child care providers, custodians and librarians." Announced endorsement of Sen. Clinton on Oct. 31, 2007. campaign</t>
+  </si>
+  <si>
+    <t>Organization: President Gerald W. McEntee, Secretary-Treasurer William Lucy, Executive Board (International Vice Presidents). More than 3,500 local unions in 46 states, the District of Columbia and Puerto Rico; 61 Councils.</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>American Federation of Teachers (AFT)</t>
+  </si>
+  <si>
+    <t>Oct. 3, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/aft100307pr.html; http://p2008.org/clinton/clinton100307aft.html; http://p2008.org/photos07/photo100307.html</t>
+  </si>
+  <si>
+    <t>American Federation of Teachers (AFT) Organization: 41 member executive council. President Edward J. McElroy; Secretary-Treasurer Nat LaCour; Executive Vice President Antonia Cortese. AFT's more than 1.4 million members include pre-K through 12th grade teachers; paraprofessionals and school-related personnel (PSRP); local, state and federal employees; higher education faculty and staff; and nurses and other healthcare professionals. The union also includes more than 170,000 retiree members. More than 3,000 local affiliates nationwide; 43 state affiliates. Announced endorsement of Sen. Clinton on Oct. 3, 2007. campaign, see also photos</t>
+  </si>
+  <si>
+    <t>Organization: 41 member executive council. President Edward J. McElroy; Secretary-Treasurer Nat LaCour; Executive Vice President Antonia Cortese.</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>International Union of Bricklayers and Allied Craftworkers (BAC)</t>
+  </si>
+  <si>
+    <t>Sept. 24, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/clinton092407bac.html</t>
+  </si>
+  <si>
+    <t>International Union of Bricklayers and Allied Craftworkers (BAC) Organization: Executive Board comprises President John J. Flynn, Secretary-Treasurer James Boland and Executive Vice Presidents Ken Lambert, Gerald O’Malley and Gerard Scarano. Executive Council, the Union's highest advisory body, is made up of the Executive Board, Regional Vice Presidents from BAC's five Regions in the U.S. and Canada, IU Regional Directors, the Canadian Co-Chair, Craft Vice Presidents, and At-Large Members. Represents roughly 100,000 skilled masonry-trowel trades craftworkers. Announced endorsement of Sen. Clinton on Sept. 24, 2007. campaign</t>
+  </si>
+  <si>
+    <t>Organization: Executive Board comprises President John J. Flynn, Secretary-Treasurer James Boland and Executive Vice Presidents Ken Lambert, Gerald O’Malley and Gerard Scarano. Executive Council, the Union's highest advisory body, is made up of the Executive Board, Regional Vice Presidents from BAC's five Regions in the U.S. and Canada, IU Regional Directors, the Canadian Co-Chair, Craft Vice Presidents, and At-Large Members.</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>National Association of Letter Carriers (NALC)</t>
+  </si>
+  <si>
+    <t>Sept. 12, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/nalc091207pr.html; http://p2008.org/labor/clinton091207nalc.html; http://p2008.org/photos07/photo091207.html</t>
+  </si>
+  <si>
+    <t>National Association of Letter Carriers (NALC) Organization: 28-member Executive Council (10 Resident National officers, 3 National Trustees and 15 National Business Agents) headed by National President William H. “Bill” Young. Represents about 300,00 active and retired members, of which a bit more than two-thirds are active city delivery letter carriers employed by the U.S. Postal Service. 2,500 local branches. Announced endorsement of Sen. Clinton on Sept. 12, 2007. campaign, see also photos</t>
+  </si>
+  <si>
+    <t>Organization: 28-member Executive Council (10 Resident National officers, 3 National Trustees and 15 National Business Agents) headed by National President William H. “Bill” Young.</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>International Association of Machinists and Aerospace Workers (IAM)</t>
+  </si>
+  <si>
+    <t>Aug. 30, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/iam083007endorse.html; http://p2008.org/labor/clinton083007iam.html</t>
+  </si>
+  <si>
+    <t>International Association of Machinists and Aerospace Workers (IAM) Organization: The Executive Council consists of International President R. Thomas Buffenbarger, General Secretary-Treasurer Warren L. Mart, and 7 General Vice Presidents. Represents 730,000 members across North America including aerospace, automotive, government employees, transportation, and woodworkers. Dual endorsement of Sen. Clinton and former Gov. Huckabee announced on Aug. 30, 2007. campaign</t>
+  </si>
+  <si>
+    <t>Organization: The Executive Council consists of International President R. Thomas Buffenbarger, General Secretary-Treasurer Warren L. Mart, and 7 General Vice Presidents.</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Transportation Communications Union (TCU)</t>
+  </si>
+  <si>
+    <t>split from the International Association of Machinists and Aerospace Workers (IAM) cell</t>
+  </si>
+  <si>
+    <t>http://www.goiam.org/tcunion.cfm; http://p2008.org/labor/tcu083007pr.html; http://p2008.org/labor/clinton090607tcu.html</t>
+  </si>
+  <si>
+    <t>International Association of Machinists and Aerospace Workers (IAM) Additionally, the Transportation Communications Union (TCU), an IAM affiliate headquartered in Rockville, MD with 65,000 active and retired members ("approximately 46,000 members in the U.S., most employed in the railroad industry") announced its endorsement of Sen. Clinton on Aug. 30, 2007. [TCU affiliated with the IAM in July 2005, and a full merger is to occur no later than January 2012]. campaign</t>
+  </si>
+  <si>
+    <t>Aug. 30, 2007; July 2005; January 2012</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>United Transportation Union (UTU)</t>
+  </si>
+  <si>
+    <t>Aug. 28, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/utu082807endorse.html; http://p2008.org/labor/clinton082807utu.html</t>
+  </si>
+  <si>
+    <t>United Transportation Union (UTU) Organization: International President Paul Thompson (retiring Dec. 31). Cleveland, Ohio-based transportation labor union representing about 125,000 active and retired railroad, bus and mass transit workers in the United States and Canada. Announced endorsement of Sen. Clinton announced on Aug. 28, 2007. campaign</t>
+  </si>
+  <si>
+    <t>Organization: International President Paul Thompson (retiring Dec. 31).</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Retail, Wholesale and Department Store Union (RWDSU)</t>
+  </si>
+  <si>
+    <t>May 2007</t>
+  </si>
+  <si>
+    <t>http://www.rwdsu.info/en/</t>
+  </si>
+  <si>
+    <t>The Retail, Wholesale and Department Store Union (RWDSU), a UFCW affiliate representing 100,000 workers in the U.S. and Canada, is backing Sen. Clinton; the Executive Board voted unanimously to support Sen. Clinton at a meeting in May 2007. (Clinton addressed the RWDSU Executive Board on May 11, 2007. In 1999 the union was the first to endorse her campaign for Senate).</t>
+  </si>
+  <si>
+    <t>May 2007; May 11, 2007</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Barack Obama</t>
+  </si>
+  <si>
+    <t>United Mine Workers of America (UMWA)</t>
+  </si>
+  <si>
+    <t>May 21, 2008</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>John Edwards</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/umwa052108pr.html</t>
+  </si>
+  <si>
+    <t>United Mine Workers of America (UMWA) Organization: President Cecil Roberts and Secretary-Treasurer Dan Kane. Originally endorsed Sen. Edwards in Sept. 2007. Represents 105,000 active and retired coal miners, municipal employees, health care workers and manufacturing workers in North America. UMWA announced its endorsemet of Sen. Obama on May 21, 2008.</t>
+  </si>
+  <si>
+    <t>OBAMA</t>
+  </si>
+  <si>
+    <t>Organization: President Cecil Roberts and Secretary-Treasurer Dan Kane.</t>
+  </si>
+  <si>
+    <t>Sept. 2007; May 21, 2008</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>United Steelworkers (USW)</t>
+  </si>
+  <si>
+    <t>May 15, 2008</t>
+  </si>
+  <si>
+    <t>usw051508pr.html</t>
+  </si>
+  <si>
+    <t>United Steelworkers (USW) Organization: International President Leo W. Gerard and International Secretary-Treasurer James D. English head up the International Executive Board. Originally endorsed Sen. Edwards in Sept. 2007. Represents 1.2 million members and retirees ("the largest industrial union in North America"). United Steelworkers announced its endorsement of Sen. Obama on May 15, 2008, the day after Edwards endorsed Obama.</t>
+  </si>
+  <si>
+    <t>Organization: International President Leo W. Gerard and International Secretary-Treasurer James D. English head up the International Executive Board.</t>
+  </si>
+  <si>
+    <t>Sept. 2007; May 15, 2008</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>American Federation of Government Employees</t>
+  </si>
+  <si>
+    <t>May 9, 2008</t>
+  </si>
+  <si>
+    <t>afge050908pr.html</t>
+  </si>
+  <si>
+    <t>American Federation of Government Employees Organization: National President John Gage. The largest federal employee union representing 600,000 federal and D.C. government workers nationwide and overseas. Announced endorsement of Sen. Obama on May 9, 2008.</t>
+  </si>
+  <si>
+    <t>Organization: National President John Gage.</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Change to Win</t>
+  </si>
+  <si>
+    <t>Feb. 21, 2008</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/changetowin022108pr.html</t>
+  </si>
+  <si>
+    <t>Change to Win Organization: 7 affiliated unions. Chair Anna Berger. Announced endorsement of Sen. Obama on Feb. 21, 2008. Carpenters, LIUNA and UFW abstained.</t>
+  </si>
+  <si>
+    <t>Organization: 7 affiliated unions. Chair Anna Berger.</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Teamsters</t>
+  </si>
+  <si>
+    <t>Feb. 20, 2008</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/teamsters022008pr.html</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Teamsters Organization: General President James P. Hoffa; General Secretary-Treasurer Tom Keegel; General Executive Board consisting of 22 Vice Presidents. Represents 1.4 million workers who work in areas including warehouse, parcel, freight, public employees and industrial trades. Announced endorsement of Sen. Obama on Feb. 20, 2008.</t>
+  </si>
+  <si>
+    <t>Organization: General President James P. Hoffa; General Secretary-Treasurer Tom Keegel; General Executive Board consisting of 22 Vice Presidents.</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Boilermakers</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/boilermakers022008pr.html</t>
+  </si>
+  <si>
+    <t>International Brotherhood of Boilermakers Organization: International President Newton B. Jones; International Secretary-Treasurer William T. Creeden; five International Vice Presidents. Headquartered in Kansas City, KS, the International Brotherhood of Boilermakers, Iron Ship Builders, Blacksmiths, Forgers and Helpers, AFL-CIO represents 65,000 members. Announced endorsement of Sen. Obama on Feb. 20, 2008.</t>
+  </si>
+  <si>
+    <t>Organization: International President Newton B. Jones; International Secretary-Treasurer William T. Creeden; five International Vice Presidents.</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Service Employees International Union (SEIU)</t>
+  </si>
+  <si>
+    <t>Feb. 15, 2008</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/seiu100807pr.html; http://p2008.org/photos07/seiu0907/seiu0907main.html</t>
+  </si>
+  <si>
+    <t>Service Employees International Union (SEIU) Organization: President Andy Stern, Secretary-Treasurer Anna Burger; Executive Vice Presidents Mary Kay Henry, Gerry Hudson, Eliseo Medina, andTom Woodruff. SEIU represents 1.9 million members and and 50,000 retirees in the United States, Canada, and Puerto Rico focused in hospital systems and long term care (900,000 members), property services (225,000 members), and public services (850,000 members). On Oct. 8, 2007 the SEIU announced that its local unions would decide on presidential primary endorsements on a state-by-state basis, with decisions announced no earlier than Oct. 15, 2007. Local unions did endorse, opting for Edwards (CA, ID, IA, MI, MT, MN, OH, OR, WA, WV; MA; NH), Obama (IL, MO-KS, WI) and Clinton (SEIU Locals 1199 and 32BJ). On Feb. 15, 2008 in a conference call the SEIU executive board endorsed Sen. Obama. see also photos</t>
+  </si>
+  <si>
+    <t>Organization: President Andy Stern, Secretary-Treasurer Anna Burger; Executive Vice Presidents Mary Kay Henry, Gerry Hudson, Eliseo Medina, andTom Woodruff.</t>
+  </si>
+  <si>
+    <t>Oct. 8, 2007; Oct. 15, 2007; Feb. 15, 2008</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>United Food and Commercial Workers Union (UFCW)</t>
+  </si>
+  <si>
+    <t>Feb. 14, 2008</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/ufcw021408pr.html</t>
+  </si>
+  <si>
+    <t>United Food and Commercial Workers Union (UFCW) Organization: International President Joseph T. Hansen; International Secretary-Treasurer Anthony M. Perrone; Executive Vice Presidents William T. McDonough, Patrick J. O'Neill, and Wayne E. Hanley. Represents more than 1.3 million workers, primarily in the retail and meatpacking, food processing and poultry industries. Announced endorsement of Sen. Obama on Feb. 14, 2008.</t>
+  </si>
+  <si>
+    <t>Organization: International President Joseph T. Hansen; International Secretary-Treasurer Anthony M. Perrone; Executive Vice Presidents William T. McDonough, Patrick J. O'Neill, and Wayne E. Hanley.</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Transport Workers Union (TWU)</t>
+  </si>
+  <si>
+    <t>Feb. 1, 2008</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/twu020108pr.html</t>
+  </si>
+  <si>
+    <t>Transport Workers Union (TWU) Organization: International President James C. Little. Originally endorsed Sen. Edwards in Sept. 2007. Represents 200,000 active and retired members. Announced endorsement of Sen. Obama on Feb. 1, 2008.</t>
+  </si>
+  <si>
+    <t>Organization: International President James C. Little.</t>
+  </si>
+  <si>
+    <t>Sept. 2007; Feb. 1, 2008</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>UNITE HERE</t>
+  </si>
+  <si>
+    <t>Jan. 9, 2008</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/unitehere010908pr.html</t>
+  </si>
+  <si>
+    <t>UNITE HERE Organization: General President Bruce Raynor. President, Hospitality Industry John W. Wilhelm. Represents nearly half a million workers in the hospitality, gaming, apparel, textile, retail, distribution, food service and laundry industries in North America. Held its founding convention July 9, 2004. Announced endorsement of Sen. Obama on Jan. 9, 2008.</t>
+  </si>
+  <si>
+    <t>Organization: General President Bruce Raynor. President, Hospitality Industry John W. Wilhelm.</t>
+  </si>
+  <si>
+    <t>July 9, 2004; Jan. 9, 2008</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>United Association (UA - Plumbers and Pipe Fitters)</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/ua010908pr.html</t>
+  </si>
+  <si>
+    <t>United Association (UA - Plumbers and Pipe Fitters) Organization: International President William P. Hite, General Secretary-Treasurer Patrick R. Perno. Represents approximately 340,000 members who belong to over 300 individual local unions across North America. Announced endorsement of Sen. Obama on Jan. 9, 2008.</t>
+  </si>
+  <si>
+    <t>Organization: International President William P. Hite, General Secretary-Treasurer Patrick R. Perno.</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Chris Dodd</t>
+  </si>
+  <si>
+    <t>International Association of Fire Fighters (IAFF)</t>
+  </si>
+  <si>
+    <t>Aug. 29, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/iaff082907pr.html; http://p2008.org/labor/iaff082907endorse.html; http://p2008.org/labor/dodd082907iaff.html; http://p2008.org/interestg08/iaff050807pr.html; http://p2008.org/iaff031407/iaff0307main.html</t>
+  </si>
+  <si>
+    <t>International Association of Fire Fighters (IAFF) Organization: The Executive Board is chaired by General President Harold A. Schaitberger and includes Secretary-Treasurer Vinnie Bollon and 16 regional Vice Presidents. Represents more than 281,000 full-time professional fire fighters and paramedics. More than 3,100 affiliates and their members protect communities in every state in the United States and in Canada. Announced (2) endorsement of Sen. Dodd on Aug. 29, 2007. campaign -May 10-11, 2007...IAFF Federation of State and Provincial Professional Fire Fighters meeting in Portsmouth, NH (press release). -March 14, 2007..."IAFF Bipartisan 2008 Presidential Forum" during International Association of Fire Fighters (IAFF) Legislative Conference in Washington, DC. -The Jan.-Feb. 2007 issue of International Fire Fighter contained a message from IAFF General President Harold A. Schaitberger outlining endorsement criteria.</t>
+  </si>
+  <si>
+    <t>DODD</t>
+  </si>
+  <si>
+    <t>Organization: The Executive Board is chaired by General President Harold A. Schaitberger and includes Secretary-Treasurer Vinnie Bollon and 16 regional Vice Presidents.</t>
+  </si>
+  <si>
+    <t>Aug. 29, 2007; March 14, 2007; Feb. 2007</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Sept. 6, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/twu090607pr.html; http://p2008.org/labor/edwards090607twu.html</t>
+  </si>
+  <si>
+    <t>Transport Workers Union (TWU) Organization: International President James C. Little. Represents 200,000 active and retired members. Announced endorsement of former Sen. Edwards on Sept. 6, 2007. campaign</t>
+  </si>
+  <si>
+    <t>EDWARDS</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Sept. 3, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/usw090307pr.html; http://p2008.org/labor/edwards090307usw.html; http://p2008.org/interestg08/usw070207pr.html</t>
+  </si>
+  <si>
+    <t>United Steelworkers (USW) Organization: International President Leo W. Gerard and International Secretary-Treasurer James D. English head up the International Executive Board. Represents 1.2 million members and retirees ("the largest industrial union in North America"). Announced endorsement of former Sen. Edwards on Sept. 3, 2007. campaign -July 5-6, 2007...Four Democratic candidates spoke at the United Steelworkers (USW) Presidential Candidates' Forum on Renewing American Manufacturing at Crowne Plaza Cleveland City Centre Hotel in Cleveland, OH.</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/edwards090307usw.html</t>
+  </si>
+  <si>
+    <t>United Mine Workers of America (UMWA) Organization: President Cecil Roberts and Secretary-Treasurer Dan Kane. Represents 105,000 active and retired coal miners, municipal employees, health care workers and manufacturing workers in North America. Announced endorsement of former Sen. Edwards on Sept. 3, 2007. campaign</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>United Brotherhood of Carpenters and Joiners of America (UBC)</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/carpenters083007pr.html; http://p2008.org/labor/edwards083007carp.html</t>
+  </si>
+  <si>
+    <t>United Brotherhood of Carpenters and Joiners of America (UBC) Represents more than 520,000 men and women throughout the building-trades industries including carpenters, cabinetmakers, millwrights, piledrivers, lathers, framers, floorlayers, roofers, drywallers, and workers in forest-products and related industries. Announced endorsement of former Sen. Edwards on Aug. 30, 2007. campaign</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>2008R</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Mike Huckabee</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/iam083007endorse.html; http://p2008.org/labor/huck083007iam.html</t>
+  </si>
+  <si>
+    <t>International Association of Machinists and Aerospace Workers (IAM) Organization: The Executive Council consists of International President R. Thomas Buffenbarger, General Secretary-Treasurer Warren L. Mart, and 7 General Vice Presidents. Represents 730,000 members across North America including aerospace, automotive, government employees, transportation, and woodworkers. Announced dual endorsement of Sen. Clinton and former Gov. Huckabee on Aug. 30, 2007. campaign</t>
+  </si>
+  <si>
+    <t>HUCKABEE</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Joe Biden</t>
+  </si>
+  <si>
+    <t>Delaware Plumbers &amp; Pipefitters Local Union 74</t>
+  </si>
+  <si>
+    <t>State/Local Labor Organization</t>
+  </si>
+  <si>
+    <t>Dec. 21, 2007</t>
+  </si>
+  <si>
+    <t>Sen. Joe Biden received the endorsement of Delaware Plumbers &amp; Pipefitters Local Union 74 on Dec. 21, 2007. Business Manager is John J. Czerwinski.</t>
+  </si>
+  <si>
+    <t>State/Local</t>
+  </si>
+  <si>
+    <t>BIDEN</t>
+  </si>
+  <si>
+    <t>Sen. Joe Biden</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>United Auto Workers (UAW) Delaware State CAP Council</t>
+  </si>
+  <si>
+    <t>Dec. 18, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/biden/biden121807pr.html</t>
+  </si>
+  <si>
+    <t>Sen. Joe Biden received the endorsement of the United Auto Workers (UAW) Delaware State CAP Council on Dec. 18, 2007. There are over 5,000 active and 7,000 retired members in Delaware; CAP Council President is Richard McDonaugh, Jr.. campaign</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Delaware Communications Workers of America (CWA), Local 13101</t>
+  </si>
+  <si>
+    <t>Dec. 17, 2007</t>
+  </si>
+  <si>
+    <t>Sen. Joe Biden received the endorsement of the Delaware Communications Workers of America (CWA), Local 13101 on Dec. 17, 2007. CWA Local 13101 Executive President is Bud Speakman.</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Plumbing, Pipefitting, and Refrigeration Workers UA Local 525</t>
+  </si>
+  <si>
+    <t>Dec. 14, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/biden/biden121407prnv.html</t>
+  </si>
+  <si>
+    <t>The Plumbing, Pipefitting, and Refrigeration Workers UA Local 525 [Nevada] endorsed Sen. Joe Biden on Dec. 14, 2007. Business Manager is Brett McCoy. campaign</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Delaware State Education Association (DSEA)</t>
+  </si>
+  <si>
+    <t>Oct. 18, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/biden/biden101807dsea.html</t>
+  </si>
+  <si>
+    <t>The Biden campaign announced the endorsement of the 11,000 member Delaware State Education Association (DSEA) on Oct. 18, 2007. DSEA is the state affiliate of the 2.6 million member National Education Association. campaign</t>
+  </si>
+  <si>
+    <t>Biden</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Delaware State AFL-CIO</t>
+  </si>
+  <si>
+    <t>June 14, 2007</t>
+  </si>
+  <si>
+    <t>The Delaware State AFL-CIO announced its unanimous endorsement of Sen. Joe Biden for president on June 14, 2007.</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>SEIU Local 1199</t>
+  </si>
+  <si>
+    <t>announced together in one paragraph</t>
+  </si>
+  <si>
+    <t>The Clinton campaign announced the endorsements of SEIU Locals 1199 and 32BJ on Dec. 14, 2007. "SEIU 1199 is the largest and fastest growing health care union in the country, with more than 300,000 members in Massachusetts, Maryland, New York and Washington, DC... SEIU 32BJ is the largest property service workers union in the country with more than 100,000 members in New York, New Jersey, Connecticut, Pennsylvania, Maryland, Virginia and Washington, DC."</t>
+  </si>
+  <si>
+    <t>Clinton</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>SEIU Local 32BJ</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>NEA-NH</t>
+  </si>
+  <si>
+    <t>Dec. 6, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/clinton120607prnh.html</t>
+  </si>
+  <si>
+    <t>NEA-NH announced its endorsement of Sen. Hillary Clinton on Dec. 6, 2007. NEA-NH is the largest union in New Hampshire with 16,000 members. President is Rhonda Wesolowski. campaign</t>
+  </si>
+  <si>
+    <t>Sen. Hillary Clinton</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>IATSE Stage Employees Local 720 in Las Vegas</t>
+  </si>
+  <si>
+    <t>http://p2008.org/clinton/clinton112907prnv.html</t>
+  </si>
+  <si>
+    <t>IATSE Stage Employees Local 720 in Las Vegas announced its endorsement of Sen. Hillary Clinton on Nov. 29, 2007. Local 720 includes approximately 4,500 members and affiliated workers involved with the convention and trade show industry, theatrical productions and live entertainment events in southern Nevada. Local 720 President is Hal Ritzer. campaign</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>CSEA Local 1000 AFSCME</t>
+  </si>
+  <si>
+    <t>July 25, 2007</t>
+  </si>
+  <si>
+    <t>CSEA Local 1000 AFSCME, which bills itself as "New York's leading union" and claims 265,000 members, announced its endorsement of Sen. Hillary Clinton on July 25, 2007.</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>UFCW Local 1500</t>
+  </si>
+  <si>
+    <t>June 21, 2007</t>
+  </si>
+  <si>
+    <t>The Clinton exploratory committee announced the endorsement of UFCW Local 1500 (represents more than 22,000 members working in the grocery industry across the metropolitan New York area; President Bruce Both) on June 21, 2007.</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>International Union of Operating Engineers Local 324</t>
+  </si>
+  <si>
+    <t>June 15, 2007</t>
+  </si>
+  <si>
+    <t>The Clinton exploratory committee announced the endorsement of Michigan-based International Union of Operating Engineers Local 324 on June 15, 2007.</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Communications Workers of America in Nevada</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/edw120607prcwa.html</t>
+  </si>
+  <si>
+    <t>Communications Workers of America in Nevada announced its endorsement of Sen. John Edwards on Dec. 6, 2007; CWA Local 9413 President is Chuck Benway and Executive Vice President is Liz Sorenson. campaign</t>
+  </si>
+  <si>
+    <t>Sen. John Edwards</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Iowa Postal Workers Union</t>
+  </si>
+  <si>
+    <t>http://p2008.org/edwards/edw101807pripwu.html</t>
+  </si>
+  <si>
+    <t>The Edwards campaign announced the endorsement of the Iowa Postal Workers Union, representing more than 3,000 workers in all 99 counties, on Oct. 18, 2007. The Iowa Postal Workers Union is the statewide branch of the AFL-CIO-affiliated American Postal Workers Union. campaign</t>
+  </si>
+  <si>
+    <t>Edwards</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>New Hampshire State Employees' Association (SEIU local 1984)</t>
+  </si>
+  <si>
+    <t>http://p2008.org/edwards/edwards103107nhsea.html</t>
+  </si>
+  <si>
+    <t>The New Hampshire State Employees' Association (SEIU local 1984) announced its endorsement of Sen. John Edwards on Oct. 31, 2007. campaign</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Massachusetts Council of the Service Employees International Union</t>
+  </si>
+  <si>
+    <t>The Massachusetts Council of the Service Employees International Union (90,000 members) announced its endorsement of Sen. John Edwards on Oct. 18, 2007.</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>SEIU California State Council</t>
+  </si>
+  <si>
+    <t>Oct. 15, 2007</t>
+  </si>
+  <si>
+    <t>656,000 members; one of ten SEIU state councils announced together</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/edw101507pr.html</t>
+  </si>
+  <si>
+    <t>Ten SEIU State Councils announced their endorsement of Sen. John Edwards on Oct. 15, 2007. California (656,000 members), Idaho (450 members), Iowa (2,000 members), Michigan (70,000 members), Montana (500 members), Minnesota (28,000 members), Ohio (22,000 members), Oregon (46,000 members), Washington (103,000 members) and West Virginia (4,000 members). campaign</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>SEIU Idaho State Council</t>
+  </si>
+  <si>
+    <t>450 members; one of ten SEIU state councils announced together</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>SEIU Iowa State Council</t>
+  </si>
+  <si>
+    <t>2,000 members; one of ten SEIU state councils announced together</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>SEIU Michigan State Council</t>
+  </si>
+  <si>
+    <t>70,000 members; one of ten SEIU state councils announced together</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>SEIU Montana State Council</t>
+  </si>
+  <si>
+    <t>500 members; one of ten SEIU state councils announced together</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>SEIU Minnesota State Council</t>
+  </si>
+  <si>
+    <t>28,000 members; one of ten SEIU state councils announced together</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>SEIU Ohio State Council</t>
+  </si>
+  <si>
+    <t>22,000 members; one of ten SEIU state councils announced together</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>SEIU Oregon State Council</t>
+  </si>
+  <si>
+    <t>46,000 members; one of ten SEIU state councils announced together</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>SEIU Washington State Council</t>
+  </si>
+  <si>
+    <t>103,000 members; one of ten SEIU state councils announced together</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>SEIU West Virginia State Council</t>
+  </si>
+  <si>
+    <t>4,000 members; one of ten SEIU state councils announced together</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Oregon AFSCME</t>
+  </si>
+  <si>
+    <t>March 15, 2008</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/orafscme031508.html</t>
+  </si>
+  <si>
+    <t>Oregon AFSCME announced its endorsement of Sen. Barack Obama on March 15, 2008.</t>
+  </si>
+  <si>
+    <t>Sen. Barack Obama</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>Oregon Education Association</t>
+  </si>
+  <si>
+    <t>March 8, 2008</t>
+  </si>
+  <si>
+    <t>The Oregon Education Association announced its endorsement of Sen. Barack Obama on March 8, 2008.</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>The Council of Social Security Field Office Locals, Council 220 AFGE</t>
+  </si>
+  <si>
+    <t>Feb. 29, 2008</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/afge220022908pr.html</t>
+  </si>
+  <si>
+    <t>The Council of Social Security Field Office Locals, Council 220 AFGE announced its endorsement of Sen. Barack Obama on Feb. 29, 2008.</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>Feb. 5, 2008</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/seiuwa020508pr.html</t>
+  </si>
+  <si>
+    <t>SEIU Washington State Council, which had endorsed Sen. John Edwards, announced its endorsement of Sen. Barack Obama on Feb. 5, 2008, four days before the Washington caucuses.</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>SEIU California State Council, which had endorsed Sen. John Edwards, endorsed Sen. Barack Obama on Feb. 1, 2008, two days after Edwards announced the end of his campaign and four days before the California primary. Represents more than 650,000 members in California, including healthcare workers, nurses, janitors, librarians, homecare workers, security officers, technicians, social workers and others. Annelle Grajeda, president.</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>Culinary Workers Union Local 226</t>
+  </si>
+  <si>
+    <t>http://p2008.org/obama/obama010908prnv.html</t>
+  </si>
+  <si>
+    <t>Culinary Workers Union Local 226 endorsed Sen. Barack Obama on Jan. 9, 2008. The Culinary Workers Union is the largest and most politically active union in Nevada comprising 60,000 members who work at casinos on the Las Vegas Strip, downtown Las Vegas and in Reno. campaign</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>Illinois Education Association-NEA (IEA)</t>
+  </si>
+  <si>
+    <t>The Illinois Education Association-NEA (IEA) voted to recommend Sen. Barack Obama on Dec. 6, 2007. (IEA represents more than 130,000 Illinois elementary and secondary teachers, higher education faculty and staff, educational support professionals, retired educators and college students preparing to become teachers. President is Ken Swanson).</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>AFSCME Council 31</t>
+  </si>
+  <si>
+    <t>Dec. 1, 2007</t>
+  </si>
+  <si>
+    <t>afscme31120107pr.html</t>
+  </si>
+  <si>
+    <t>AFSCME Council 31 announced its endorsement of Sen. Barack Obama on Dec. 1, 2007.</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>United Auto Workers Region 4</t>
+  </si>
+  <si>
+    <t>Nov. 15, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/obama111507pruaw.html</t>
+  </si>
+  <si>
+    <t>Delegates of United Auto Workers Region 4 endorsed Sen. Barack Obama on Nov. 15, 2007. UAW Region 4 represents 64,000 active and 122,000 retirees in Iowa, Illinois, Minnesota, Wisconsin, Montana, Nebraska, North Dakota, South Dakota, and Wyoming, including 30,000 members and retirees in Iowa. Dennis Williams is director. campaign</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>SEIU Wisconsin State Council</t>
+  </si>
+  <si>
+    <t>Oct. 26, 2007</t>
+  </si>
+  <si>
+    <t>SEIU Wisconsin State Council endorsed Sen. Barack Obama on Oct. 26, 2007, citing his "commitment to expanding access to affordable health care and to protecting workers' rights." (State Council President is Dian Palmer; the union has 15,000-plus members).</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>Missouri-Kansas State Council of the Service Employees International Union</t>
+  </si>
+  <si>
+    <t>Missouri-Kansas State Council of the Service Employees International Union (represents more than 15,000 members in both states) endorsed Sen. Barack Obama on Oct. 18, 2007. Sherwin Carroll is president of the council.</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>SEIU Illinois State Council</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/obama101507prseiu.html</t>
+  </si>
+  <si>
+    <t>SEIU Illinois State Council announced its endorsement of Sen. Barack Obama on Oct. 15, 2007. campaign</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>New York City Correction Officers' Benevolent Association (COBA)</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/obama092407pr.html</t>
+  </si>
+  <si>
+    <t>The New York City Correction Officers' Benevolent Association (COBA) (represents 9,000 unionized members in New York City and is the largest municipal jail union in the country) endorsed Sen. Barack Obama on Sept. 24, 2007. campaign</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Bill Richardson</t>
+  </si>
+  <si>
+    <t>Plasterers and Cement Masons Local 797</t>
+  </si>
+  <si>
+    <t>Plasterers and Cement Masons Local 797 (represents 2,000 members in southern Nevada, business manager Marc Leavitt).</t>
+  </si>
+  <si>
+    <t>RICHARDSON</t>
+  </si>
+  <si>
+    <t>dual endorsement of Clinton and Huckabee on Aug. 30, 2007</t>
+  </si>
+  <si>
+    <t>edited</t>
+  </si>
+  <si>
+    <t>added note of dual endorsement</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>NV</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>added state from endorsement raw text</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>WA</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>WV</t>
+  </si>
+  <si>
+    <t>OH</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>added</t>
+  </si>
+  <si>
+    <t>favorite sister resolution included in page notes</t>
+  </si>
+  <si>
+    <t>New York State AFL-CIO</t>
+  </si>
+  <si>
+    <t>May 3, 2007</t>
+  </si>
+  <si>
+    <t>http://p2008.org/labor/nyaflcio050307.html</t>
+  </si>
+  <si>
+    <t>new-1</t>
+  </si>
+  <si>
+    <t>On May 3, 2007 the New York State AFL-CIO issued a resolution declaring Sen. Hillary Clinton its “favorite sister” in the presidential campaign.</t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>issued a resolution declaring Sen. Hillary Clinton its "favorite sister"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="@"/>
-  </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1237,12 +1331,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1265,15 +1361,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1555,38 +1661,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y274"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="40.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="8.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="40.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="32.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="21.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="10.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="16.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="40.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="13.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="18.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="18.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="40.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="11.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="80.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="13.71" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="17.71" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="22.71" hidden="0" customWidth="1"/>
-    <col min="24" max="24" width="40.71" hidden="0" customWidth="1"/>
-    <col min="25" max="25" width="40.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="6" width="8.6640625" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="8" max="8" width="40.6640625" customWidth="1"/>
+    <col min="9" max="9" width="32.6640625" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="40.6640625" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="16" max="17" width="18.6640625" customWidth="1"/>
+    <col min="18" max="18" width="40.6640625" customWidth="1"/>
+    <col min="19" max="19" width="11.6640625" customWidth="1"/>
+    <col min="20" max="20" width="80.6640625" customWidth="1"/>
+    <col min="21" max="21" width="13.6640625" customWidth="1"/>
+    <col min="22" max="22" width="17.6640625" customWidth="1"/>
+    <col min="23" max="23" width="22.6640625" customWidth="1"/>
+    <col min="24" max="25" width="40.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1663,7 +1766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,7 +1829,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
@@ -1789,7 +1892,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>47</v>
       </c>
@@ -1852,7 +1955,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>53</v>
       </c>
@@ -1915,7 +2018,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>59</v>
       </c>
@@ -1978,7 +2081,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>65</v>
       </c>
@@ -2041,7 +2144,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>71</v>
       </c>
@@ -2104,7 +2207,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>77</v>
       </c>
@@ -2167,7 +2270,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>83</v>
       </c>
@@ -2230,7 +2333,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>89</v>
       </c>
@@ -2293,7 +2396,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>95</v>
       </c>
@@ -2356,15 +2459,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>402</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>27</v>
@@ -2390,7 +2493,9 @@
       <c r="M13" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="N13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="O13" s="1" t="s">
         <v>34</v>
       </c>
@@ -2419,7 +2524,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>107</v>
       </c>
@@ -2482,7 +2587,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>113</v>
       </c>
@@ -2545,7 +2650,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>119</v>
       </c>
@@ -2606,7 +2711,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>125</v>
       </c>
@@ -2673,7 +2778,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>136</v>
       </c>
@@ -2740,7 +2845,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>143</v>
       </c>
@@ -2803,7 +2908,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>149</v>
       </c>
@@ -2866,7 +2971,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>155</v>
       </c>
@@ -2929,7 +3034,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>161</v>
       </c>
@@ -2992,7 +3097,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>166</v>
       </c>
@@ -3055,7 +3160,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>173</v>
       </c>
@@ -3118,7 +3223,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>179</v>
       </c>
@@ -3185,7 +3290,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>186</v>
       </c>
@@ -3248,7 +3353,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>193</v>
       </c>
@@ -3311,7 +3416,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>198</v>
       </c>
@@ -3374,7 +3479,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>207</v>
       </c>
@@ -3437,7 +3542,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>212</v>
       </c>
@@ -3500,7 +3605,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>216</v>
       </c>
@@ -3563,7 +3668,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>219</v>
       </c>
@@ -3624,15 +3729,15 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>223</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>26</v>
+        <v>402</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>224</v>
@@ -3658,7 +3763,9 @@
       <c r="M33" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="N33" s="1"/>
+      <c r="N33" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="O33" s="1" t="s">
         <v>34</v>
       </c>
@@ -3687,15 +3794,15 @@
         <v>103</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>230</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>27</v>
@@ -3716,7 +3823,9 @@
         <v>233</v>
       </c>
       <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>420</v>
+      </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1" t="s">
         <v>234</v>
@@ -3748,15 +3857,15 @@
         <v>234</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>239</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>27</v>
@@ -3777,7 +3886,9 @@
         <v>233</v>
       </c>
       <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>420</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
         <v>241</v>
@@ -3811,15 +3922,15 @@
         <v>241</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>244</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>27</v>
@@ -3840,7 +3951,9 @@
         <v>233</v>
       </c>
       <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
+      <c r="K36" s="1" t="s">
+        <v>420</v>
+      </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
         <v>246</v>
@@ -3872,15 +3985,15 @@
         <v>246</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>248</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>27</v>
@@ -3901,7 +4014,9 @@
         <v>233</v>
       </c>
       <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
         <v>250</v>
@@ -3935,15 +4050,15 @@
         <v>250</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>253</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>27</v>
@@ -3964,7 +4079,9 @@
         <v>233</v>
       </c>
       <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
+      <c r="K38" s="1" t="s">
+        <v>420</v>
+      </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
         <v>255</v>
@@ -3998,15 +4115,15 @@
         <v>255</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>259</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>27</v>
@@ -4027,7 +4144,9 @@
         <v>233</v>
       </c>
       <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
+      <c r="K39" s="1" t="s">
+        <v>420</v>
+      </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1" t="s">
         <v>261</v>
@@ -4059,7 +4178,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>263</v>
       </c>
@@ -4122,7 +4241,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>268</v>
       </c>
@@ -4185,15 +4304,15 @@
         <v>250</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>270</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>27</v>
@@ -4214,7 +4333,9 @@
         <v>233</v>
       </c>
       <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
+      <c r="K42" s="1" t="s">
+        <v>403</v>
+      </c>
       <c r="L42" s="1"/>
       <c r="M42" s="1" t="s">
         <v>272</v>
@@ -4248,15 +4369,15 @@
         <v>272</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>276</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>27</v>
@@ -4277,7 +4398,9 @@
         <v>233</v>
       </c>
       <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
+      <c r="K43" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1" t="s">
         <v>67</v>
@@ -4311,15 +4434,15 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>280</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>27</v>
@@ -4340,7 +4463,9 @@
         <v>233</v>
       </c>
       <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
+      <c r="K44" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
         <v>282</v>
@@ -4372,15 +4497,15 @@
         <v>282</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>284</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>27</v>
@@ -4401,7 +4526,9 @@
         <v>233</v>
       </c>
       <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
+      <c r="K45" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="L45" s="1"/>
       <c r="M45" s="1" t="s">
         <v>286</v>
@@ -4433,15 +4560,15 @@
         <v>286</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>288</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>27</v>
@@ -4462,7 +4589,9 @@
         <v>233</v>
       </c>
       <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
+      <c r="K46" s="1" t="s">
+        <v>406</v>
+      </c>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="s">
         <v>290</v>
@@ -4494,15 +4623,15 @@
         <v>290</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>292</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>27</v>
@@ -4523,7 +4652,9 @@
         <v>233</v>
       </c>
       <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
+      <c r="K47" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="L47" s="1"/>
       <c r="M47" s="1" t="s">
         <v>272</v>
@@ -4557,15 +4688,15 @@
         <v>272</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>297</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>27</v>
@@ -4586,7 +4717,9 @@
         <v>233</v>
       </c>
       <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
+      <c r="K48" s="1" t="s">
+        <v>417</v>
+      </c>
       <c r="L48" s="1"/>
       <c r="M48" s="1" t="s">
         <v>255</v>
@@ -4620,15 +4753,15 @@
         <v>255</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>302</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>27</v>
@@ -4649,7 +4782,9 @@
         <v>233</v>
       </c>
       <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
+      <c r="K49" s="1" t="s">
+        <v>403</v>
+      </c>
       <c r="L49" s="1"/>
       <c r="M49" s="1" t="s">
         <v>79</v>
@@ -4683,15 +4818,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>306</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>27</v>
@@ -4712,7 +4847,9 @@
         <v>233</v>
       </c>
       <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
+      <c r="K50" s="1" t="s">
+        <v>419</v>
+      </c>
       <c r="L50" s="1"/>
       <c r="M50" s="1" t="s">
         <v>255</v>
@@ -4744,15 +4881,15 @@
         <v>255</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>309</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>27</v>
@@ -4773,7 +4910,9 @@
         <v>233</v>
       </c>
       <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
+      <c r="K51" s="1" t="s">
+        <v>410</v>
+      </c>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
         <v>311</v>
@@ -4809,15 +4948,15 @@
         <v>311</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>315</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>27</v>
@@ -4838,7 +4977,9 @@
         <v>233</v>
       </c>
       <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
+      <c r="K52" s="1" t="s">
+        <v>418</v>
+      </c>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="s">
         <v>311</v>
@@ -4874,15 +5015,15 @@
         <v>311</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>318</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>27</v>
@@ -4903,7 +5044,9 @@
         <v>233</v>
       </c>
       <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
+      <c r="K53" s="1" t="s">
+        <v>417</v>
+      </c>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
         <v>311</v>
@@ -4939,15 +5082,15 @@
         <v>311</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>321</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>27</v>
@@ -4968,7 +5111,9 @@
         <v>233</v>
       </c>
       <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
+      <c r="K54" s="1" t="s">
+        <v>406</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1" t="s">
         <v>311</v>
@@ -5004,15 +5149,15 @@
         <v>311</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>324</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>27</v>
@@ -5033,7 +5178,9 @@
         <v>233</v>
       </c>
       <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
+      <c r="K55" s="1" t="s">
+        <v>416</v>
+      </c>
       <c r="L55" s="1"/>
       <c r="M55" s="1" t="s">
         <v>311</v>
@@ -5069,15 +5216,15 @@
         <v>311</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>327</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>27</v>
@@ -5098,7 +5245,9 @@
         <v>233</v>
       </c>
       <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
+      <c r="K56" s="1" t="s">
+        <v>415</v>
+      </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="s">
         <v>311</v>
@@ -5134,15 +5283,15 @@
         <v>311</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>330</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>27</v>
@@ -5163,7 +5312,9 @@
         <v>233</v>
       </c>
       <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
+      <c r="K57" s="1" t="s">
+        <v>414</v>
+      </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
         <v>311</v>
@@ -5199,15 +5350,15 @@
         <v>311</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>333</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>27</v>
@@ -5228,7 +5379,9 @@
         <v>233</v>
       </c>
       <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
+      <c r="K58" s="1" t="s">
+        <v>408</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
         <v>311</v>
@@ -5264,15 +5417,15 @@
         <v>311</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>336</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>27</v>
@@ -5293,7 +5446,9 @@
         <v>233</v>
       </c>
       <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
+      <c r="K59" s="1" t="s">
+        <v>409</v>
+      </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1" t="s">
         <v>311</v>
@@ -5329,15 +5484,15 @@
         <v>311</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>339</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>27</v>
@@ -5358,7 +5513,9 @@
         <v>233</v>
       </c>
       <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
+      <c r="K60" s="1" t="s">
+        <v>413</v>
+      </c>
       <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
         <v>311</v>
@@ -5394,15 +5551,15 @@
         <v>311</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>342</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>27</v>
@@ -5423,7 +5580,9 @@
         <v>233</v>
       </c>
       <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
+      <c r="K61" s="1" t="s">
+        <v>408</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
         <v>344</v>
@@ -5457,15 +5616,15 @@
         <v>344</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>348</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>27</v>
@@ -5486,7 +5645,9 @@
         <v>233</v>
       </c>
       <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
+      <c r="K62" s="1" t="s">
+        <v>408</v>
+      </c>
       <c r="L62" s="1"/>
       <c r="M62" s="1" t="s">
         <v>350</v>
@@ -5518,7 +5679,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>352</v>
       </c>
@@ -5581,15 +5742,15 @@
         <v>354</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>357</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>27</v>
@@ -5610,7 +5771,9 @@
         <v>233</v>
       </c>
       <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
+      <c r="K64" s="1" t="s">
+        <v>409</v>
+      </c>
       <c r="L64" s="1"/>
       <c r="M64" s="1" t="s">
         <v>358</v>
@@ -5648,15 +5811,15 @@
         <v>358</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>361</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>27</v>
@@ -5677,7 +5840,9 @@
         <v>233</v>
       </c>
       <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
+      <c r="K65" s="1" t="s">
+        <v>410</v>
+      </c>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
         <v>181</v>
@@ -5713,15 +5878,15 @@
         <v>181</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>363</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>27</v>
@@ -5742,7 +5907,9 @@
         <v>233</v>
       </c>
       <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
+      <c r="K66" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="L66" s="1"/>
       <c r="M66" s="1" t="s">
         <v>188</v>
@@ -5776,15 +5943,15 @@
         <v>188</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>367</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>27</v>
@@ -5805,7 +5972,9 @@
         <v>233</v>
       </c>
       <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
+      <c r="K67" s="1" t="s">
+        <v>411</v>
+      </c>
       <c r="L67" s="1"/>
       <c r="M67" s="1" t="s">
         <v>272</v>
@@ -5837,7 +6006,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>370</v>
       </c>
@@ -5900,7 +6069,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>375</v>
       </c>
@@ -5963,15 +6132,15 @@
         <v>377</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>380</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>27</v>
@@ -5992,7 +6161,9 @@
         <v>233</v>
       </c>
       <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
+      <c r="K70" s="1" t="s">
+        <v>412</v>
+      </c>
       <c r="L70" s="1"/>
       <c r="M70" s="1" t="s">
         <v>382</v>
@@ -6024,7 +6195,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>384</v>
       </c>
@@ -6085,15 +6256,15 @@
         <v>255</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>387</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>27</v>
@@ -6114,7 +6285,9 @@
         <v>233</v>
       </c>
       <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
+      <c r="K72" s="1" t="s">
+        <v>411</v>
+      </c>
       <c r="L72" s="1"/>
       <c r="M72" s="1" t="s">
         <v>311</v>
@@ -6148,15 +6321,15 @@
         <v>311</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>391</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>27</v>
@@ -6177,7 +6350,9 @@
         <v>233</v>
       </c>
       <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
+      <c r="K73" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="L73" s="1"/>
       <c r="M73" s="1" t="s">
         <v>91</v>
@@ -6211,15 +6386,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>395</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>26</v>
+        <v>401</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>27</v>
@@ -6240,7 +6415,9 @@
         <v>233</v>
       </c>
       <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
+      <c r="K74" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
@@ -6266,34 +6443,66 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
     </row>
-    <row r="75">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
+      <c r="K75" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="L75" s="1"/>
-      <c r="M75" s="1"/>
-      <c r="N75" s="1"/>
-      <c r="O75" s="1"/>
+      <c r="M75" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="P75" s="1"/>
       <c r="Q75" s="1"/>
-      <c r="R75" s="1"/>
+      <c r="R75" s="3" t="s">
+        <v>425</v>
+      </c>
       <c r="S75" s="1"/>
-      <c r="T75" s="1"/>
+      <c r="T75" t="s">
+        <v>427</v>
+      </c>
       <c r="U75" s="1"/>
-      <c r="V75" s="1"/>
+      <c r="V75" s="1" t="s">
+        <v>428</v>
+      </c>
       <c r="W75" s="1"/>
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -6320,7 +6529,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -6347,7 +6556,7 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6374,7 +6583,7 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6401,7 +6610,7 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6428,7 +6637,7 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6455,7 +6664,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -6482,7 +6691,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -6509,7 +6718,7 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -6536,7 +6745,7 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -6563,7 +6772,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -6590,7 +6799,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -6617,7 +6826,7 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -6644,7 +6853,7 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -6671,7 +6880,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -6698,7 +6907,7 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -6725,7 +6934,7 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -6752,7 +6961,7 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -6779,7 +6988,7 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -6806,7 +7015,7 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -6833,7 +7042,7 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -6860,7 +7069,7 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -6887,7 +7096,7 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -6914,7 +7123,7 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -6941,7 +7150,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -6968,7 +7177,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -6995,7 +7204,7 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7022,7 +7231,7 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7049,7 +7258,7 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7076,7 +7285,7 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7103,7 +7312,7 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7130,7 +7339,7 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7157,7 +7366,7 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7184,7 +7393,7 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7211,7 +7420,7 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7238,7 +7447,7 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7265,7 +7474,7 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7292,7 +7501,7 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7319,7 +7528,7 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7346,7 +7555,7 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7373,7 +7582,7 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7400,7 +7609,7 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7427,7 +7636,7 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7454,7 +7663,7 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -7481,7 +7690,7 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -7508,7 +7717,7 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -7535,7 +7744,7 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -7562,7 +7771,7 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -7589,7 +7798,7 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -7616,7 +7825,7 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -7643,7 +7852,7 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -7670,7 +7879,7 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -7697,7 +7906,7 @@
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -7724,7 +7933,7 @@
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -7751,7 +7960,7 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -7778,7 +7987,7 @@
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -7805,7 +8014,7 @@
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -7832,7 +8041,7 @@
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -7859,7 +8068,7 @@
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -7886,7 +8095,7 @@
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -7913,7 +8122,7 @@
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -7940,7 +8149,7 @@
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -7967,7 +8176,7 @@
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -7994,7 +8203,7 @@
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -8021,7 +8230,7 @@
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -8048,7 +8257,7 @@
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -8075,7 +8284,7 @@
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -8102,7 +8311,7 @@
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -8129,7 +8338,7 @@
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -8156,7 +8365,7 @@
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -8183,7 +8392,7 @@
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -8210,7 +8419,7 @@
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -8237,7 +8446,7 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -8264,7 +8473,7 @@
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -8291,7 +8500,7 @@
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -8318,7 +8527,7 @@
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -8345,7 +8554,7 @@
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -8372,7 +8581,7 @@
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -8399,7 +8608,7 @@
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -8426,7 +8635,7 @@
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -8453,7 +8662,7 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -8480,7 +8689,7 @@
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -8507,7 +8716,7 @@
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -8534,7 +8743,7 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -8561,7 +8770,7 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -8588,7 +8797,7 @@
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -8615,7 +8824,7 @@
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -8642,7 +8851,7 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -8669,7 +8878,7 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -8696,7 +8905,7 @@
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -8723,7 +8932,7 @@
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -8750,7 +8959,7 @@
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -8777,7 +8986,7 @@
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -8804,7 +9013,7 @@
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -8831,7 +9040,7 @@
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -8858,7 +9067,7 @@
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -8885,7 +9094,7 @@
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -8912,7 +9121,7 @@
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -8939,7 +9148,7 @@
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -8966,7 +9175,7 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -8993,7 +9202,7 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -9020,7 +9229,7 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -9047,7 +9256,7 @@
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -9074,7 +9283,7 @@
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -9101,7 +9310,7 @@
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -9128,7 +9337,7 @@
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -9155,7 +9364,7 @@
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -9182,7 +9391,7 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -9209,7 +9418,7 @@
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -9236,7 +9445,7 @@
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -9263,7 +9472,7 @@
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -9290,7 +9499,7 @@
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -9317,7 +9526,7 @@
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -9344,7 +9553,7 @@
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -9371,7 +9580,7 @@
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -9398,7 +9607,7 @@
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -9425,7 +9634,7 @@
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -9452,7 +9661,7 @@
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -9479,7 +9688,7 @@
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -9506,7 +9715,7 @@
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -9533,7 +9742,7 @@
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -9560,7 +9769,7 @@
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -9587,7 +9796,7 @@
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -9614,7 +9823,7 @@
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -9641,7 +9850,7 @@
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -9668,7 +9877,7 @@
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -9695,7 +9904,7 @@
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -9722,7 +9931,7 @@
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -9749,7 +9958,7 @@
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -9776,7 +9985,7 @@
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -9803,7 +10012,7 @@
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -9830,7 +10039,7 @@
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -9857,7 +10066,7 @@
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -9884,7 +10093,7 @@
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -9911,7 +10120,7 @@
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -9938,7 +10147,7 @@
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -9965,7 +10174,7 @@
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -9992,7 +10201,7 @@
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -10019,7 +10228,7 @@
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -10046,7 +10255,7 @@
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -10073,7 +10282,7 @@
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -10100,7 +10309,7 @@
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -10127,7 +10336,7 @@
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -10154,7 +10363,7 @@
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -10181,7 +10390,7 @@
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -10208,7 +10417,7 @@
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
     </row>
-    <row r="221">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -10235,7 +10444,7 @@
       <c r="X221" s="1"/>
       <c r="Y221" s="1"/>
     </row>
-    <row r="222">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -10262,7 +10471,7 @@
       <c r="X222" s="1"/>
       <c r="Y222" s="1"/>
     </row>
-    <row r="223">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -10289,7 +10498,7 @@
       <c r="X223" s="1"/>
       <c r="Y223" s="1"/>
     </row>
-    <row r="224">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -10316,7 +10525,7 @@
       <c r="X224" s="1"/>
       <c r="Y224" s="1"/>
     </row>
-    <row r="225">
+    <row r="225" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -10343,7 +10552,7 @@
       <c r="X225" s="1"/>
       <c r="Y225" s="1"/>
     </row>
-    <row r="226">
+    <row r="226" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -10370,7 +10579,7 @@
       <c r="X226" s="1"/>
       <c r="Y226" s="1"/>
     </row>
-    <row r="227">
+    <row r="227" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -10397,7 +10606,7 @@
       <c r="X227" s="1"/>
       <c r="Y227" s="1"/>
     </row>
-    <row r="228">
+    <row r="228" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -10424,7 +10633,7 @@
       <c r="X228" s="1"/>
       <c r="Y228" s="1"/>
     </row>
-    <row r="229">
+    <row r="229" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -10451,7 +10660,7 @@
       <c r="X229" s="1"/>
       <c r="Y229" s="1"/>
     </row>
-    <row r="230">
+    <row r="230" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -10478,7 +10687,7 @@
       <c r="X230" s="1"/>
       <c r="Y230" s="1"/>
     </row>
-    <row r="231">
+    <row r="231" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -10505,7 +10714,7 @@
       <c r="X231" s="1"/>
       <c r="Y231" s="1"/>
     </row>
-    <row r="232">
+    <row r="232" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -10532,7 +10741,7 @@
       <c r="X232" s="1"/>
       <c r="Y232" s="1"/>
     </row>
-    <row r="233">
+    <row r="233" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -10559,7 +10768,7 @@
       <c r="X233" s="1"/>
       <c r="Y233" s="1"/>
     </row>
-    <row r="234">
+    <row r="234" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -10586,7 +10795,7 @@
       <c r="X234" s="1"/>
       <c r="Y234" s="1"/>
     </row>
-    <row r="235">
+    <row r="235" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -10613,7 +10822,7 @@
       <c r="X235" s="1"/>
       <c r="Y235" s="1"/>
     </row>
-    <row r="236">
+    <row r="236" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -10640,7 +10849,7 @@
       <c r="X236" s="1"/>
       <c r="Y236" s="1"/>
     </row>
-    <row r="237">
+    <row r="237" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -10667,7 +10876,7 @@
       <c r="X237" s="1"/>
       <c r="Y237" s="1"/>
     </row>
-    <row r="238">
+    <row r="238" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -10694,7 +10903,7 @@
       <c r="X238" s="1"/>
       <c r="Y238" s="1"/>
     </row>
-    <row r="239">
+    <row r="239" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -10721,7 +10930,7 @@
       <c r="X239" s="1"/>
       <c r="Y239" s="1"/>
     </row>
-    <row r="240">
+    <row r="240" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -10748,7 +10957,7 @@
       <c r="X240" s="1"/>
       <c r="Y240" s="1"/>
     </row>
-    <row r="241">
+    <row r="241" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -10775,7 +10984,7 @@
       <c r="X241" s="1"/>
       <c r="Y241" s="1"/>
     </row>
-    <row r="242">
+    <row r="242" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -10802,7 +11011,7 @@
       <c r="X242" s="1"/>
       <c r="Y242" s="1"/>
     </row>
-    <row r="243">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -10829,7 +11038,7 @@
       <c r="X243" s="1"/>
       <c r="Y243" s="1"/>
     </row>
-    <row r="244">
+    <row r="244" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -10856,7 +11065,7 @@
       <c r="X244" s="1"/>
       <c r="Y244" s="1"/>
     </row>
-    <row r="245">
+    <row r="245" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -10883,7 +11092,7 @@
       <c r="X245" s="1"/>
       <c r="Y245" s="1"/>
     </row>
-    <row r="246">
+    <row r="246" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -10910,7 +11119,7 @@
       <c r="X246" s="1"/>
       <c r="Y246" s="1"/>
     </row>
-    <row r="247">
+    <row r="247" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -10937,7 +11146,7 @@
       <c r="X247" s="1"/>
       <c r="Y247" s="1"/>
     </row>
-    <row r="248">
+    <row r="248" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -10964,7 +11173,7 @@
       <c r="X248" s="1"/>
       <c r="Y248" s="1"/>
     </row>
-    <row r="249">
+    <row r="249" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -10991,7 +11200,7 @@
       <c r="X249" s="1"/>
       <c r="Y249" s="1"/>
     </row>
-    <row r="250">
+    <row r="250" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -11018,7 +11227,7 @@
       <c r="X250" s="1"/>
       <c r="Y250" s="1"/>
     </row>
-    <row r="251">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -11045,7 +11254,7 @@
       <c r="X251" s="1"/>
       <c r="Y251" s="1"/>
     </row>
-    <row r="252">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -11072,7 +11281,7 @@
       <c r="X252" s="1"/>
       <c r="Y252" s="1"/>
     </row>
-    <row r="253">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -11099,7 +11308,7 @@
       <c r="X253" s="1"/>
       <c r="Y253" s="1"/>
     </row>
-    <row r="254">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -11126,7 +11335,7 @@
       <c r="X254" s="1"/>
       <c r="Y254" s="1"/>
     </row>
-    <row r="255">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -11153,7 +11362,7 @@
       <c r="X255" s="1"/>
       <c r="Y255" s="1"/>
     </row>
-    <row r="256">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -11180,7 +11389,7 @@
       <c r="X256" s="1"/>
       <c r="Y256" s="1"/>
     </row>
-    <row r="257">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -11207,7 +11416,7 @@
       <c r="X257" s="1"/>
       <c r="Y257" s="1"/>
     </row>
-    <row r="258">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -11234,7 +11443,7 @@
       <c r="X258" s="1"/>
       <c r="Y258" s="1"/>
     </row>
-    <row r="259">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -11261,7 +11470,7 @@
       <c r="X259" s="1"/>
       <c r="Y259" s="1"/>
     </row>
-    <row r="260">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -11288,7 +11497,7 @@
       <c r="X260" s="1"/>
       <c r="Y260" s="1"/>
     </row>
-    <row r="261">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -11315,7 +11524,7 @@
       <c r="X261" s="1"/>
       <c r="Y261" s="1"/>
     </row>
-    <row r="262">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -11342,7 +11551,7 @@
       <c r="X262" s="1"/>
       <c r="Y262" s="1"/>
     </row>
-    <row r="263">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -11369,7 +11578,7 @@
       <c r="X263" s="1"/>
       <c r="Y263" s="1"/>
     </row>
-    <row r="264">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -11396,7 +11605,7 @@
       <c r="X264" s="1"/>
       <c r="Y264" s="1"/>
     </row>
-    <row r="265">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -11423,7 +11632,7 @@
       <c r="X265" s="1"/>
       <c r="Y265" s="1"/>
     </row>
-    <row r="266">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -11450,7 +11659,7 @@
       <c r="X266" s="1"/>
       <c r="Y266" s="1"/>
     </row>
-    <row r="267">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -11477,7 +11686,7 @@
       <c r="X267" s="1"/>
       <c r="Y267" s="1"/>
     </row>
-    <row r="268">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -11504,7 +11713,7 @@
       <c r="X268" s="1"/>
       <c r="Y268" s="1"/>
     </row>
-    <row r="269">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -11531,7 +11740,7 @@
       <c r="X269" s="1"/>
       <c r="Y269" s="1"/>
     </row>
-    <row r="270">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -11558,7 +11767,7 @@
       <c r="X270" s="1"/>
       <c r="Y270" s="1"/>
     </row>
-    <row r="271">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -11585,7 +11794,7 @@
       <c r="X271" s="1"/>
       <c r="Y271" s="1"/>
     </row>
-    <row r="272">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -11612,7 +11821,7 @@
       <c r="X272" s="1"/>
       <c r="Y272" s="1"/>
     </row>
-    <row r="273">
+    <row r="273" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -11639,7 +11848,7 @@
       <c r="X273" s="1"/>
       <c r="Y273" s="1"/>
     </row>
-    <row r="274">
+    <row r="274" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -11667,8 +11876,8 @@
       <c r="Y274" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y74"/>
+  <autoFilter ref="A1:Y74" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>